--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -41,26 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,22 +143,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="11" t="n">
         <v>31.7</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="11" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -798,45 +798,47 @@
       </c>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>18.4</v>
+        <v>2.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>29.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>30.6</v>
+        <v>23.8</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n">
+        <v>851.8</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="X4" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="Y4" s="3" t="n">
-        <v>76.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
@@ -852,21 +854,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="9" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>8.800000000000001</v>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>14.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17.3</v>
+        <v>15.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
@@ -878,38 +886,44 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>262</v>
+        <v>14.6</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="O5" s="3" t="n"/>
+        <v>13.8</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>31.6</v>
+      </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>92.7</v>
+        <v>2</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S5" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>7.2</v>
+      </c>
       <c r="T5" s="3" t="n">
-        <v>70.2</v>
+        <v>14.4</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
+        <v>18.6</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="X5" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="Y5" s="3" t="n">
         <v>6.8</v>
       </c>
@@ -927,70 +941,69 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 5
-</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>15.2</v>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>14.4</v>
+        <v>1.3</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>20.8</v>
+        <v>1.1</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>91.2</v>
+        <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="Q6" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="R6" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>26.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>7.2</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="U6" s="3" t="n"/>
+        <v>81.2</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>61.5</v>
+      </c>
       <c r="V6" s="3" t="n">
-        <v>23.9</v>
+        <v>5.1</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>74.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>4.2</v>
@@ -1009,70 +1022,76 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="9" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>10.6</v>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>-93.3</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>-52.7</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>-73</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.8</v>
+        <v>0.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>20.3</v>
+        <v>1.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>17.5</v>
+        <v>2.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O7" s="3" t="n"/>
+        <v>13.8</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>31.6</v>
+      </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>19.5</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n">
-        <v>22.9</v>
+        <v>26.8</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>21.2</v>
+        <v>41.3</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.6</v>
+        <v>2.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>86.2</v>
+        <v>4.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>11.4</v>
+        <v>4</v>
       </c>
       <c r="Z7" s="3" t="n"/>
       <c r="AA7" s="3" t="inlineStr">
@@ -1089,67 +1108,71 @@
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
-      <c r="D8" s="9" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>8.4</v>
+      <c r="D8" s="11" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>10.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.3</v>
+        <v>17.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.4</v>
+        <v>15.8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>18.9</v>
+        <v>4.4</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="P8" s="3" t="n">
-        <v>1.1</v>
+        <v>22.5</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>25.8</v>
+        <v>20.1</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S8" s="8" t="n">
-        <v>66.2</v>
+        <v>3.5</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>5.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>21.4</v>
+        <v>0.9</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>21.4</v>
+        <v>19.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>59.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="inlineStr">
@@ -1166,71 +1189,67 @@
         </is>
       </c>
       <c r="C9" s="3" t="n"/>
-      <c r="D9" s="9" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>57.8</v>
+      <c r="D9" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>8.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>57.8</v>
+        <v>1.3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9.6</v>
+        <v>1.3</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
+        <v>2.1</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44.2</v>
+        <v>18.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>20.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>11.4</v>
+        <v>2.1</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>94.2</v>
+      </c>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>190.9</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>24.8</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n">
-        <v>318.6</v>
+        <v>2.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>48.8</v>
+        <v>4.2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.6</v>
+        <v>1.4</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>110.8</v>
+        <v>2.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>23.6</v>
+        <v>2.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>382.2</v>
+        <v>5.2</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>7.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1247,67 +1266,69 @@
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>23.7</v>
+      <c r="D10" s="11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>4.5</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>19.6</v>
+        <v>5.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>16.2</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>591.2</v>
-      </c>
-      <c r="O10" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>52.1</v>
+      </c>
       <c r="P10" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>22.3</v>
-      </c>
+        <v>19.1</v>
+      </c>
+      <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n">
-        <v>24.5</v>
+        <v>6.3</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>23.8</v>
+        <v>48.8</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>26.9</v>
+        <v>19.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>23.6</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>16.2</v>
+        <v>38.6</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>31.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="inlineStr">
@@ -1324,67 +1345,69 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="9" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>23.7</v>
+      <c r="D11" s="15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>43.7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>81</v>
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M11" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>92.59999999999999</v>
+      </c>
       <c r="N11" s="3" t="n">
-        <v>2.1</v>
+        <v>94.2</v>
       </c>
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>28.4</v>
+        <v>2</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>26.7</v>
+        <v>2</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>24.8</v>
+        <v>4.2</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>25.2</v>
+        <v>2.2</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>26.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>22.2</v>
+        <v>6.2</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1401,67 +1424,75 @@
         </is>
       </c>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>18.5</v>
+      <c r="D12" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>1.9</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>22.4</v>
+        <v>23.8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+577
+</t>
+        </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>19</v>
+        <v>8.5</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="N12" s="3" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>29.6</v>
+      </c>
       <c r="O12" s="3" t="n">
-        <v>90.2</v>
+        <v>0.1</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.1</v>
+        <v>6.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>934.8</v>
+        <v>8.4</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S12" s="3" t="n"/>
+        <v>25.1</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>28.5</v>
+      </c>
       <c r="T12" s="3" t="n">
-        <v>0.1</v>
+        <v>61.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>24.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>22.9</v>
+        <v>4.8</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>26.8</v>
+        <v>25.4</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>81.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="3" t="inlineStr">
@@ -1478,67 +1509,71 @@
         </is>
       </c>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E13" s="9" t="n">
+      <c r="D13" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="F13" s="9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>19.9</v>
-      </c>
       <c r="M13" s="3" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="O13" s="3" t="n"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="P13" s="3" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>24.3</v>
+        <v>93.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>22.9</v>
+        <v>2</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>62.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="U13" s="3" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V13" s="3" t="n">
-        <v>21.8</v>
+        <v>2.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>24.4</v>
+        <v>46.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1555,71 +1590,69 @@
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="9" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>16.5</v>
+      <c r="D14" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>18.9</v>
+        <v>6.6</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>91.2</v>
+        <v>6.8</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>22.2</v>
+        <v>2</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>22.4</v>
+        <v>25.1</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.2</v>
+        <v>2.9</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>25.2</v>
-      </c>
+        <v>6.3</v>
+      </c>
+      <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X14" s="8" t="n">
-        <v>83.2</v>
+        <v>24.9</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="Z14" s="3" t="n"/>
       <c r="AA14" s="3" t="inlineStr">
@@ -1636,67 +1669,71 @@
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>22.5</v>
+      <c r="D15" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>22.6</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>16.5</v>
+        <v>98.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.9</v>
+        <v>1.5</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
+        <v>18.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>23.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>46.6</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>25.7</v>
+        <v>22.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U15" s="3" t="n"/>
+        <v>3.8</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V15" s="3" t="n">
-        <v>22.8</v>
+        <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>26.4</v>
+        <v>12.4</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>17.2</v>
+        <v>85.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>51.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z15" s="3" t="n"/>
       <c r="AA15" s="3" t="inlineStr">
@@ -1713,69 +1750,67 @@
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="14" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>116.6</v>
+      <c r="D16" s="16" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>2.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>13.9</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>92.3</v>
+        <v>1.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
+        <v>2.7</v>
       </c>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n">
-        <v>951.3</v>
+        <v>19.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>953.2</v>
-      </c>
+        <v>24.7</v>
+      </c>
+      <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n">
-        <v>5.3</v>
+        <v>92.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.2</v>
+        <v>32.7</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>26.6</v>
+        <v>12.4</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>22.9</v>
+        <v>42.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>18.2</v>
+        <v>5.2</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>9.1</v>
+        <v>1</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1841.7</v>
+        <v>2.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>20.9</v>
+        <v>2.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>24.4</v>
+        <v>26.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.2</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1792,65 +1827,71 @@
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>81.09999999999999</v>
+      <c r="D17" s="16" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.5</v>
+        <v>2.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="L17" s="3" t="n">
-        <v>19.9</v>
+        <v>10.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.2</v>
+        <v>4.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q17" s="3" t="n"/>
+        <v>12.7</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>42.9</v>
+      </c>
       <c r="R17" s="8" t="n">
-        <v>26.6</v>
+        <v>46.6</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>26.6</v>
+        <v>5.7</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>22.9</v>
+        <v>16.2</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>704.3</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>2.9</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>85.3</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>151</v>
+        <v>0.2</v>
       </c>
       <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
@@ -1867,67 +1908,71 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n">
-        <v>25.1</v>
+      <c r="D18" s="15" t="n">
+        <v>1.8</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>24.9</v>
+        <v>24.3</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>2.3</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>9.6</v>
+        <v>48.1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="I18" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Q18" s="8" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="U18" s="3" t="n"/>
       <c r="V18" s="3" t="n">
-        <v>21.5</v>
+        <v>4.1</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>24.8</v>
+        <v>14.6</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>82.2</v>
+        <v>48.3</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="inlineStr">
@@ -1944,69 +1989,71 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="12" t="n">
-        <v>3</v>
+      <c r="D19" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>13.8</v>
+        <v>8.5</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>12.9</v>
+        <v>9.6</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.4</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J19" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>6262.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V19" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n">
-        <v>981.2</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>20.8</v>
-      </c>
       <c r="W19" s="3" t="n">
-        <v>254.3</v>
+        <v>4.8</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>85.2</v>
+        <v>28.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2023,69 +2070,71 @@
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>12.9</v>
+      <c r="D20" s="11" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>17.6</v>
+        <v>46.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>28.3</v>
+        <v>2.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N20" s="3" t="n"/>
+        <v>85.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>91.2</v>
+      </c>
       <c r="O20" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>19.9</v>
+        <v>32.4</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>19.8</v>
+        <v>2</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>20.2</v>
+        <v>4</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>20.2</v>
+        <v>2.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>1.9</v>
+        <v>258.3</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2102,69 +2151,71 @@
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="9" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>9.6</v>
+      <c r="D21" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>12.6</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>19.2</v>
+        <v>18.3</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>80.09999999999999</v>
+        <v>28</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>292.2</v>
+        <v>393.2</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>92.2</v>
+        <v>927.2</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>19.2</v>
+        <v>12.8</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.9</v>
+        <v>18.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>22</v>
+        <v>25.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="U21" s="3" t="n"/>
+        <v>20.2</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>29.2</v>
+      </c>
       <c r="V21" s="3" t="n">
-        <v>19.9</v>
+        <v>2.2</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>90.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2181,71 +2232,71 @@
         </is>
       </c>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>23.2</v>
+      <c r="D22" s="11" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>23.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.2</v>
+        <v>3.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>13.9</v>
+        <v>1.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="K22" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>21</v>
-      </c>
       <c r="Q22" s="3" t="n">
-        <v>28.5</v>
+        <v>2.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>29.9</v>
+        <v>2.2</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>26.2</v>
+        <v>42.8</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>80.2</v>
+        <v>15.3</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="inlineStr">
@@ -2262,71 +2313,71 @@
         </is>
       </c>
       <c r="C23" s="3" t="n"/>
-      <c r="D23" s="14" t="n">
-        <v>194.8</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>119.2</v>
+      <c r="D23" s="16" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>2.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>57.9</v>
+        <v>1.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>68.8</v>
+        <v>15.2</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>14</v>
+        <v>389.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>96.2</v>
+        <v>3.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>185.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>18.6</v>
+        <v>2.9</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.8</v>
+        <v>1393.2</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.4</v>
+        <v>26</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4.9</v>
+        <v>41.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>119.9</v>
+        <v>1.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>536</v>
+        <v>25.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>37.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>102.6</v>
+        <v>12.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.4</v>
+        <v>22.9</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>427.8</v>
+        <v>230.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.7</v>
+        <v>0.8</v>
       </c>
       <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="3" t="inlineStr">
@@ -2343,66 +2394,68 @@
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="14" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E24" s="14" t="n">
+      <c r="D24" s="16" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>282.8</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="F24" s="14" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n">
-        <v>98.8</v>
-      </c>
       <c r="M24" s="3" t="n">
-        <v>19.2</v>
+        <v>1.7</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>391.2</v>
+        <v>20</v>
       </c>
       <c r="P24" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>23.5</v>
-      </c>
       <c r="X24" s="3" t="n">
-        <v>85.2</v>
+        <v>80.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
@@ -2422,71 +2475,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="9" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>24.9</v>
+      <c r="D25" s="15" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11.1</v>
+        <v>5.3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.9</v>
+        <v>2.2</v>
       </c>
       <c r="I25" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="X25" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>0.8</v>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 1
+</t>
+        </is>
       </c>
       <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2503,69 +2559,71 @@
         </is>
       </c>
       <c r="C26" s="3" t="n"/>
-      <c r="D26" s="9" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>23.9</v>
+      <c r="D26" s="15" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>2.8</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I26" s="3" t="n"/>
+        <v>16.8</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J26" s="3" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="K26" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>24</v>
-      </c>
       <c r="X26" s="3" t="n">
-        <v>80.2</v>
+        <v>8.5</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2582,69 +2640,71 @@
         </is>
       </c>
       <c r="C27" s="3" t="n"/>
-      <c r="D27" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>9.9</v>
+      <c r="D27" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>12.9</v>
       </c>
       <c r="I27" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="L27" s="3" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>16.2</v>
+        <v>19.1</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>10</v>
+        <v>93.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R27" s="8" t="n">
-        <v>39.3</v>
+        <v>25.8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>5.6</v>
+        <v>0.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v>34.9</v>
+        <v>6.2</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>22</v>
+        <v>2.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>28.2</v>
+        <v>24.5</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>53.2</v>
+        <v>6.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>8.6</v>
+        <v>0.8</v>
       </c>
       <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2661,71 +2721,71 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="9" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>24.3</v>
+      <c r="D28" s="15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>2.4</v>
       </c>
       <c r="G28" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="I28" s="3" t="n">
-        <v>3.2</v>
+        <v>19.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>16.8</v>
+        <v>18</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>958.4</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>92.2</v>
+        <v>29.1</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>11.4</v>
+        <v>2.6</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>21.2</v>
+        <v>2.1</v>
       </c>
       <c r="S28" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>853.9</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="Y28" s="3" t="n">
         <v>14.5</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>2.3</v>
       </c>
       <c r="Z28" s="3" t="n"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2742,71 +2802,71 @@
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
-      <c r="D29" s="9" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>19.7</v>
+      <c r="D29" s="11" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>16.8</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
+        <v>35.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.2</v>
+        <v>16.8</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>651.1</v>
+        <v>682.5</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>90.2</v>
+        <v>92.8</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>451.6</v>
+        <v>2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="R29" s="8" t="n">
-        <v>26.4</v>
+        <v>1.8</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W29" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>82.59999999999999</v>
+        <v>2.2</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32.4</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2823,71 +2883,71 @@
         </is>
       </c>
       <c r="C30" s="3" t="n"/>
-      <c r="D30" s="9" t="n">
-        <v>152</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>119.7</v>
+      <c r="D30" s="16" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>4.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>58.8</v>
+        <v>1.2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>11.3</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>92.8</v>
+        <v>18.5</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>4.5</v>
+        <v>3908.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>91.2</v>
+        <v>2.4</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.1</v>
+        <v>26.4</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>26.9</v>
+        <v>12.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>25.3</v>
+        <v>26.4</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>922.2</v>
+        <v>322.2</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>44.2</v>
+        <v>49.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>82.8</v>
+        <v>134.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>20.8</v>
+        <v>1042.6</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>22.9</v>
+        <v>14.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>17.2</v>
+        <v>322.5</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>6.5</v>
+        <v>24.4</v>
       </c>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2904,69 +2964,71 @@
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
-      <c r="D31" s="9" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>19.8</v>
+      <c r="D31" s="16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>58.2</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>13.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L31" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>18.5</v>
+      <c r="M31" s="8" t="n">
+        <v>751.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>19.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>4</v>
+        <v>452.6</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>39.7</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>2644.4</v>
+        <v>28.9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>15.5</v>
+        <v>48.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>23.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>22.9</v>
+        <v>2.8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>25.3</v>
+        <v>2.9</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>3</v>
+        <v>63.5</v>
       </c>
       <c r="Z31" s="3" t="n"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -2983,67 +3045,71 @@
         </is>
       </c>
       <c r="C32" s="3" t="n"/>
-      <c r="D32" s="12" t="n">
-        <v>32.18</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>14.5</v>
+      <c r="D32" s="15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>72.5</v>
+        <v>0.9</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>91.2</v>
+      </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>28.9</v>
+        <v>26.4</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>26.8</v>
+        <v>2.6</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>35.3</v>
+        <v>3.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>20.4</v>
+        <v>23.6</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>23</v>
+        <v>2.2</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>27.4</v>
+        <v>0.9</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>80.3</v>
+        <v>84.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3060,69 +3126,71 @@
         </is>
       </c>
       <c r="C33" s="3" t="n"/>
-      <c r="D33" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E33" s="9" t="n">
+      <c r="D33" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="9" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>17.9</v>
-      </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>19.8</v>
+        <v>5.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>81.8</v>
+        <v>12.5</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="O33" s="3" t="n"/>
+        <v>87.90000000000001</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>24.8</v>
+        <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>27.8</v>
+        <v>24.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>22.9</v>
+        <v>2.3</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>4.8</v>
+        <v>48.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>21.5</v>
+        <v>24.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>86.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3138,43 +3206,51 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="9" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>12.7</v>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18</v>
+        <v>1.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.2</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="8" t="n">
-        <v>81.2</v>
+        <v>0.9</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>78.2</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>928.2</v>
+        <v>1.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>24.8</v>
@@ -3183,25 +3259,25 @@
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>24.6</v>
+        <v>29.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>68.2</v>
+        <v>63.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>24.2</v>
+        <v>2.5</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>62.8</v>
+        <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>13.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z34" s="3" t="n"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3218,69 +3294,67 @@
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>89.40000000000001</v>
+      <c r="D35" s="15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>2.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>27.4</v>
+        <v>25.8</v>
       </c>
       <c r="G35" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>18.2</v>
-      </c>
       <c r="I35" s="3" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M35" s="3" t="n"/>
+        <v>12.1</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="N35" s="8" t="n">
         <v>92.2</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>928.2</v>
-      </c>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n">
-        <v>27.9</v>
+        <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>33.6</v>
+        <v>53.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>25.8</v>
+        <v>45.1</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>23.9</v>
+        <v>4</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>22.8</v>
+        <v>6.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3296,68 +3370,76 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="n">
-        <v>23.6</v>
+        <v>30.4</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>25.8</v>
+        <v>18.4</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>2.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>15.6</v>
+        <v>18</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>454.2</v>
+        <v>18.2</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>91.8</v>
+        <v>2.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="8" t="n">
-        <v>8090.2</v>
-      </c>
-      <c r="O36" s="3" t="n"/>
+      <c r="N36" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="S36" s="3" t="n">
+      <c r="R36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U36" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="T36" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="W36" s="8" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>67.59999999999999</v>
+      <c r="V36" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>58.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>37.2</v>
+        <v>0.4</v>
       </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3374,69 +3456,71 @@
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
-      <c r="D37" s="14" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>392.9</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>126.9</v>
+      <c r="D37" s="16" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>25.8</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>84634.39999999999</v>
+        <v>4.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>20.3</v>
+        <v>1.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>49.9</v>
+        <v>1.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1441.8</v>
+        <v>0.3</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>950.2</v>
-      </c>
-      <c r="O37" s="3" t="n"/>
+        <v>9450.299999999999</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>90.2</v>
+      </c>
       <c r="P37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>7.5</v>
+        <v>12.2</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>23.5</v>
+        <v>2.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>26.9</v>
+        <v>48.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>10.3</v>
+        <v>90.3</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>124.9</v>
+        <v>1242.1</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>22.2</v>
+        <v>1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>25.2</v>
+        <v>125.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>13.2</v>
+        <v>267.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>4.3</v>
+        <v>32.4</v>
       </c>
       <c r="Z37" s="3" t="n"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3453,38 +3537,36 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="12" t="n">
-        <v>421.2</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>25.4</v>
+      <c r="D38" s="15" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>26.3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>13.9</v>
+        <v>9.4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>17.4</v>
+        <v>81</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>21.3</v>
+        <v>1.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9.1</v>
+        <v>20.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>8338.4</v>
-      </c>
+        <v>85.7</v>
+      </c>
+      <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n">
-        <v>81.8</v>
+        <v>9</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.2</v>
@@ -3493,31 +3575,31 @@
         <v>2.6</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>11.6</v>
+        <v>25.8</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>23.5</v>
+        <v>2.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.9</v>
+        <v>26.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>17.9</v>
+        <v>14.1</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>24.8</v>
+        <v>48.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>21.6</v>
+        <v>2.4</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>9.9</v>
+        <v>0.4</v>
       </c>
       <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3534,67 +3616,69 @@
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n">
-        <v>32.8</v>
+      <c r="D39" s="15" t="n">
+        <v>2.3</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>51.6</v>
+        <v>18.9</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>54.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>14.1</v>
+        <v>0.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.4</v>
+        <v>12.4</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>21.3</v>
+        <v>32.3</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>9.1</v>
+        <v>4.1</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>61.2</v>
+        <v>1.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n"/>
+      <c r="M39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="N39" s="3" t="n">
-        <v>19.8</v>
+        <v>0.9</v>
       </c>
       <c r="O39" s="3" t="n"/>
       <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>28.6</v>
+        <v>18.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>61.2</v>
+        <v>6.2</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.9</v>
+        <v>24.1</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>72.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>194.4</v>
+        <v>1.9</v>
       </c>
       <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
@@ -3610,70 +3694,72 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="12" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>14.2</v>
+      <c r="C40" s="3" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>14.1</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>51</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>98.3</v>
+        <v>17</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="O40" s="3" t="n"/>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.4</v>
+        <v>6.4</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>27.8</v>
+        <v>18.2</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>27.8</v>
+        <v>4.3</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>47.8</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>21.6</v>
+        <v>2.9</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.9</v>
+        <v>2.9</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>12.6</v>
+        <v>14.5</v>
       </c>
       <c r="Z40" s="3" t="n"/>
       <c r="AA40" s="3" t="inlineStr">
@@ -3689,65 +3775,71 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="9" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="F41" s="9" t="n">
+      <c r="C41" s="3" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F41" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="9" t="n">
-        <v>12.8</v>
+      <c r="G41" s="11" t="n">
+        <v>14.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>18.5</v>
+        <v>2.9</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M41" s="3" t="n"/>
+      <c r="M41" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="N41" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="O41" s="3" t="n"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="P41" s="3" t="n">
-        <v>10.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>31.2</v>
+        <v>3.2</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.2</v>
+        <v>2.6</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.2</v>
+        <v>25.1</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>82.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3766,69 +3858,69 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>25.6</v>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>25.9</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>72.8</v>
+        <v>12.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>21</v>
+        <v>2.3</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>3.6</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>1.8</v>
+        <v>89</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>26.9</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>922.1</v>
+      <c r="N42" s="3" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>14.8</v>
+        <v>4.1</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="T42" s="3" t="n"/>
+      <c r="T42" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="U42" s="3" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>5.1</v>
+        <v>24.8</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>82.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>2.6</v>
@@ -3847,26 +3939,24 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>12.5</v>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="11" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>1.1</v>
+        <v>12.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3.6</v>
@@ -3874,37 +3964,57 @@
       <c r="K43" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L43" s="8" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
+      <c r="L43" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+745
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225778
+22
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="n"/>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+6
+</t>
+        </is>
       </c>
       <c r="T43" s="3" t="n">
-        <v>381.9</v>
+        <v>6.8</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>95.3</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>95.7</v>
+        <v>85.2</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="X43" s="8" t="n">
-        <v>27.2</v>
+        <v>3.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0.2</v>
+        <v>24.3</v>
       </c>
       <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
@@ -3921,63 +4031,78 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="9" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>-25.3</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" s="9" t="n">
-        <v>54.7</v>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4262
+7
+</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>5.4</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2429
+14
+</t>
+        </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+7
+</t>
+        </is>
       </c>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="8" t="n">
-        <v>366.3</v>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77 777
+</t>
+        </is>
       </c>
       <c r="O44" s="3" t="n"/>
-      <c r="P44" s="8" t="n">
-        <v>6.9</v>
+      <c r="P44" s="3" t="n">
+        <v>106.5</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>2.9</v>
+        <v>9.6</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="S44" s="8" t="n">
-        <v>121.3</v>
+        <v>41.8</v>
       </c>
       <c r="T44" s="3" t="n"/>
       <c r="U44" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.8</v>
+        <v>2.4</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>82.2</v>
+      <c r="X44" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>5.4</v>
+        <v>50.4</v>
       </c>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
@@ -3994,29 +4119,29 @@
         </is>
       </c>
       <c r="C45" s="3" t="n"/>
-      <c r="D45" s="9" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E45" s="9" t="n">
+      <c r="D45" s="16" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="E45" s="16" t="n">
         <v>18.7</v>
       </c>
-      <c r="F45" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G45" s="9" t="n">
-        <v>13.7</v>
+      <c r="F45" s="16" t="n">
+        <v>192.9</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>3.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2.8</v>
+        <v>69.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.1</v>
+        <v>45.5</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8.5</v>
+        <v>282.8</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>18.4</v>
@@ -4024,19 +4149,25 @@
       <c r="M45" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n">
-        <v>98.3</v>
-      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41272728
+1 8
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="3" t="n"/>
+      <c r="Q45" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="R45" s="3" t="n">
-        <v>25.7</v>
+        <v>5.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>60.2</v>
+        <v>6.2</v>
       </c>
       <c r="T45" s="3" t="n"/>
       <c r="U45" s="3" t="n">
@@ -4044,11 +4175,8 @@
       </c>
       <c r="V45" s="3" t="n"/>
       <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
+      <c r="X45" s="3" t="n">
+        <v>83.2</v>
       </c>
       <c r="Y45" s="3" t="n"/>
       <c r="Z45" s="3" t="n"/>
@@ -4065,60 +4193,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="14" t="n">
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 191
+</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="n">
         <v>32.3</v>
       </c>
-      <c r="E46" s="14" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>0.1</v>
+      <c r="E46" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>25.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+278
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q46" s="3" t="n"/>
+      <c r="R46" s="3" t="n"/>
+      <c r="S46" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U46" s="3" t="n"/>
+      <c r="T46" s="3" t="n"/>
+      <c r="U46" s="8" t="n">
+        <v>290.1</v>
+      </c>
       <c r="V46" s="8" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>150.1</v>
-      </c>
+      <c r="W46" s="3" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="X46" s="3" t="n"/>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,20 +41,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,9 +152,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -155,16 +164,25 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -777,15 +795,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="11" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>16.9</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>14.8</v>
@@ -796,51 +814,49 @@
       <c r="I4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n">
-        <v>8.9</v>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="14" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>2.1</v>
+        <v>12.4</v>
       </c>
       <c r="N4" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="O4" s="3" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="P4" s="3" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>851.8</v>
-      </c>
       <c r="S4" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T4" s="3" t="n"/>
+        <v>29.3</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>545.2</v>
+      </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W4" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+        <v>21.5</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -854,27 +870,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="11" t="n">
-        <v>31.7</v>
+        <v>26.2</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>16.9</v>
+        <v>11.4</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>14.8</v>
+        <v>18.8</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>81.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>15.3</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
@@ -886,48 +896,50 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>18.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>13.8</v>
+        <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>2</v>
+        <v>6.6</v>
+      </c>
+      <c r="Q5" s="14" t="n">
+        <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>7.2</v>
+        <v>21</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>14.4</v>
+        <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>18.6</v>
+        <v>6.5</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W5" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>26.2</v>
+        <v>23.9</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X5" s="14" t="n">
+        <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="Z5" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -941,74 +953,72 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="11" t="n">
-        <v>26.2</v>
+        <v>32.4</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>17.4</v>
+        <v>23</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>8.800000000000001</v>
+        <v>27.7</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>1.6</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>11.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>91.59999999999999</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="M6" s="14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>0</v>
+        <v>81.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.6</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2</v>
+        <v>29.5</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S6" s="8" t="n">
-        <v>7.2</v>
+        <v>24.9</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>61.5</v>
+        <v>207.4</v>
+      </c>
+      <c r="U6" s="14" t="n">
+        <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>24.4</v>
+        <v>21.2</v>
+      </c>
+      <c r="W6" s="14" t="n">
+        <v>51.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>86.2</v>
+        <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Z6" s="3" t="n"/>
+        <v>77.2</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1022,78 +1032,70 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="11" t="n">
-        <v>-93.3</v>
+        <v>30.5</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>-52.7</v>
+        <v>19.9</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>-73</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>15.2</v>
+        <v>25.2</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>20.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>31.6</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R7" s="3" t="n"/>
+        <v>20.1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="S7" s="3" t="n">
-        <v>26.8</v>
+        <v>22.9</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>14.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>41.3</v>
+        <v>21.4</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>4.8</v>
+        <v>20.6</v>
+      </c>
+      <c r="X7" s="14" t="n">
+        <v>22.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" s="3" t="n"/>
+        <v>86.2</v>
+      </c>
+      <c r="Z7" s="3" t="inlineStr"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1107,74 +1109,72 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="11" t="n">
-        <v>30.5</v>
+        <v>26.8</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>19.9</v>
+        <v>18.4</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>25.2</v>
+        <v>22.6</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>10.6</v>
+        <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.4</v>
+        <v>11.3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>15.8</v>
+        <v>14.4</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4.4</v>
+        <v>18.9</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>45.8</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>22.5</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>3.5</v>
+        <v>25.8</v>
+      </c>
+      <c r="R8" s="14" t="n">
+        <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>5.2</v>
+        <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>81.2</v>
+        <v>66.2</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>19.8</v>
+        <v>8.4</v>
+      </c>
+      <c r="V8" s="14" t="n">
+        <v>94.59999999999999</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>24.6</v>
+        <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>86.2</v>
+        <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z8" s="3" t="n"/>
+        <v>7.3</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1188,70 +1188,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="11" t="n">
-        <v>26.8</v>
+        <v>147.4</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>18.4</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>22.6</v>
+        <v>118.5</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>8.4</v>
+        <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.3</v>
+        <v>957.8</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1.3</v>
+        <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>2.1</v>
+        <v>16.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>18.9</v>
+        <v>949.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>20.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="O9" s="3" t="n"/>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="n">
+        <v>1454.6</v>
+      </c>
       <c r="P9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R9" s="3" t="n"/>
+        <v>129.4</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>1110.9</v>
+      </c>
       <c r="S9" s="3" t="n">
-        <v>2.2</v>
+        <v>142.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>4.2</v>
+        <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.4</v>
+        <v>1948.8</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>2.8</v>
+        <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>126.9</v>
+      </c>
+      <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+        <v>231.1</v>
+      </c>
+      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1265,72 +1265,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
+      <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="11" t="n">
-        <v>5.4</v>
+        <v>29.7</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3.7</v>
+        <v>17.9</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>5.8</v>
-      </c>
+        <v>23.7</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>97.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>45.8</v>
-      </c>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>52.1</v>
+        <v>91.2</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="R10" s="3" t="n"/>
+        <v>25.9</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="S10" s="3" t="n">
-        <v>6.3</v>
+        <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>48.8</v>
+        <v>164.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>23.6</v>
+        <v>24.8</v>
+      </c>
+      <c r="W10" s="14" t="n">
+        <v>282.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>38.6</v>
+        <v>25.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+        <v>216.2</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1344,72 +1342,70 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1.5</v>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="R11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>18.8</v>
+        <v>23.8</v>
+      </c>
+      <c r="S11" s="14" t="n">
+        <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>23.8</v>
+        <v>161.2</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>6.2</v>
+        <v>24.8</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X11" s="14" t="n">
+        <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+        <v>181.2</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1423,78 +1419,70 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>23.8</v>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>11.6</v>
+        <v>8.9</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1122
-577
-</t>
-        </is>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
       <c r="L12" s="3" t="n">
-        <v>8.5</v>
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>29.6</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="n">
-        <v>0.1</v>
+        <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>8.4</v>
+        <v>24.9</v>
       </c>
       <c r="R12" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="S12" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>28.5</v>
-      </c>
       <c r="T12" s="3" t="n">
-        <v>61.2</v>
+        <v>161.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>24.8</v>
+        <v>0.5</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>4.8</v>
+        <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>25.4</v>
+        <v>21.8</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2.3</v>
+        <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z12" s="3" t="n"/>
+        <v>194.5</v>
+      </c>
+      <c r="Z12" s="3" t="inlineStr"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1508,74 +1496,68 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>2.4</v>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>18.3</v>
+        <v>17.6</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="14" t="n">
+        <v>19.9</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>2.3</v>
+        <v>10.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>93.8</v>
+        <v>22.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>62.7</v>
+        <v>46.4</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>43</v>
+        <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>81.2</v>
+        <v>20</v>
+      </c>
+      <c r="X13" s="14" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+        <v>185.2</v>
+      </c>
+      <c r="Z13" s="3" t="inlineStr"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1589,72 +1571,72 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="11" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="14" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R14" s="14" t="n">
+        <v>923.4</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V14" s="14" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E14" s="15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="Y14" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+        <v>51.4</v>
+      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1668,74 +1650,70 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="11" t="n">
-        <v>26.8</v>
+        <v>28.9</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>98.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>17.8</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>2.7</v>
+        <v>16.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>92.09999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>91</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>12.7</v>
+        <v>10.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>46.6</v>
+        <v>26.6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>22.8</v>
+        <v>25.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>15.2</v>
+        <v>38.2</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>2</v>
+        <v>21.7</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>12.4</v>
+        <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>85.8</v>
+        <v>85.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z15" s="3" t="n"/>
+        <v>10.3</v>
+      </c>
+      <c r="Z15" s="3" t="inlineStr"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1749,70 +1727,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="16" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>2.5</v>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="11" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14.5</v>
+        <v>0.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>13.9</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K16" s="3" t="n"/>
+        <v>17.3</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
-        <v>19.9</v>
+        <v>2.1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>92.2</v>
+        <v>453.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>32.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>42.9</v>
+        <v>1182.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>5.2</v>
+        <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1</v>
+        <v>118.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>2.2</v>
+        <v>1949.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>26.8</v>
+        <v>1124.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>4.2</v>
+        <v>1708.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+        <v>1151</v>
+      </c>
+      <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1826,74 +1806,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="16" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>16.6</v>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>23.4</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>2.9</v>
+        <v>9.6</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>12.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="N17" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W17" s="3" t="inlineStr"/>
+      <c r="X17" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="Y17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O17" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1907,74 +1879,70 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="15" t="n">
-        <v>1.8</v>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>30.2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>2.3</v>
+        <v>13.8</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>48.1</v>
+        <v>12.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.2</v>
+        <v>46.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>91.2</v>
-      </c>
+        <v>19.2</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>12.3</v>
-      </c>
+        <v>228.8</v>
+      </c>
+      <c r="P18" s="14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="n">
-        <v>25.3</v>
+        <v>2.4</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>12.4</v>
+        <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>492.1</v>
+        <v>94.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
+      </c>
+      <c r="V18" s="14" t="n">
+        <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>14.6</v>
+        <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>48.3</v>
+        <v>85.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z18" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1988,74 +1956,66 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F19" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>9.6</v>
+      <c r="G19" s="11" t="n">
+        <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.6</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>6262.2</v>
+        <v>1.5</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>34.3</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="n">
-        <v>26.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>2</v>
+        <v>19.9</v>
+      </c>
+      <c r="R19" s="14" t="n">
+        <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>6.5</v>
+        <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>2.2</v>
+        <v>10.2</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>2.5</v>
+        <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>28.2</v>
+        <v>19.9</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <v>21.8</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2069,74 +2029,68 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="11" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>22.4</v>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.2</v>
+        <v>19.6</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>46.8</v>
+        <v>48.6</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K20" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="14" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>18.2</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>32.4</v>
+        <v>26.2</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2</v>
+        <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>5.2</v>
+        <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U20" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>2.8</v>
+      <c r="V20" s="14" t="n">
+        <v>82.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>258.3</v>
+        <v>22.1</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>83.2</v>
+        <v>23.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>9.6</v>
+      </c>
+      <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2150,74 +2104,70 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>2.9</v>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>1.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>12.6</v>
+        <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>13.9</v>
+        <v>1.9</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>73.8</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>393.2</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>927.2</v>
-      </c>
+        <v>18.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="n">
-        <v>26.2</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
+      </c>
+      <c r="R21" s="14" t="n">
+        <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>25.2</v>
+        <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>20.2</v>
+        <v>88.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>29.2</v>
+        <v>10.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>2.2</v>
+        <v>19.1</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+        <v>10.8</v>
+      </c>
+      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2231,74 +2181,72 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="11" t="n">
-        <v>38.5</v>
+        <v>29.2</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>8.5</v>
+        <v>17.8</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3.6</v>
+        <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.3</v>
+        <v>15.9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.9</v>
+        <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>2.2</v>
+        <v>28.5</v>
+      </c>
+      <c r="R22" s="14" t="n">
+        <v>39.9</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>18.4</v>
+        <v>956.2</v>
+      </c>
+      <c r="U22" s="14" t="n">
+        <v>39.9</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>42.8</v>
+        <v>22.6</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>2.9</v>
+        <v>26.8</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>15.3</v>
+        <v>80.2</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+        <v>194.7</v>
+      </c>
+      <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2312,74 +2260,68 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="16" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="18" t="n">
+        <v>1144.1</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>22.8</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>389.4</v>
+        <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.8</v>
+        <v>2464.4</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>185.1</v>
+        <v>7.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>1393.2</v>
-      </c>
+        <v>1420.9</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>26</v>
+        <v>931.6</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>41.2</v>
+        <v>1121</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.3</v>
+        <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>25.2</v>
+        <v>4.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9360.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.3</v>
+        <v>1108.4</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>12.2</v>
+        <v>102.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>22.9</v>
+        <v>197.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>230.2</v>
+        <v>927.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+        <v>12.4</v>
+      </c>
+      <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2393,74 +2335,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="16" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>3.9</v>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="18" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>829.8</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>282.8</v>
+        <v>11.4</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>98.8</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>316.4</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>8.5</v>
+        <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>360.5</v>
+        <v>27.6</v>
+      </c>
+      <c r="S24" s="14" t="n">
+        <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>13.2</v>
+        <v>728.2</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.4</v>
+        <v>6.9</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>4.6</v>
+        <v>20.5</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>0.2</v>
+        <v>22.5</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>80.2</v>
+        <v>85.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z24" s="3" t="n"/>
+      <c r="Z24" s="3" t="inlineStr"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2474,77 +2408,72 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="15" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="E25" s="3" t="n">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="11" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>183.2</v>
-      </c>
       <c r="K25" s="3" t="n">
-        <v>96.2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>97.8</v>
-      </c>
+        <v>15.2</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>22.1</v>
+        <v>1192.2</v>
+      </c>
+      <c r="P25" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>2.8</v>
+        <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>34.2</v>
+        <v>11.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>16.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22 1
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+        <v>23.2</v>
+      </c>
+      <c r="X25" s="14" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2558,74 +2487,70 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="15" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>2.8</v>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="11" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>18.8</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>53.2</v>
-      </c>
+        <v>12.6</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>26.2</v>
+        <v>91.5</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>4.6</v>
+        <v>27.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>2.9</v>
+        <v>27.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>6.8</v>
+        <v>716.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>24.2</v>
+        <v>5.9</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>8.5</v>
+        <v>24.5</v>
+      </c>
+      <c r="X26" s="14" t="n">
+        <v>86.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+        <v>0.8</v>
+      </c>
+      <c r="Z26" s="3" t="inlineStr"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2639,74 +2564,70 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>1.1</v>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="11" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12.9</v>
+        <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>93.8</v>
+        <v>49.4</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>25.8</v>
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.3</v>
+        <v>22.9</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.1</v>
+        <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>2.9</v>
+        <v>10.9</v>
+      </c>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="14" t="n">
+        <v>21.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>6.2</v>
+        <v>24</v>
+      </c>
+      <c r="X27" s="14" t="n">
+        <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z27" s="3" t="n"/>
+        <v>5.6</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2720,74 +2641,72 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>15.8</v>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="11" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>19.2</v>
+        <v>3.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>46.3</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
       <c r="O28" s="3" t="n">
-        <v>0.2</v>
+        <v>119080.9</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>2.6</v>
+        <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>2.1</v>
+        <v>23.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.5</v>
+        <v>25.6</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>853.9</v>
+        <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>2.9</v>
+        <v>18.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>2.2</v>
+        <v>21</v>
+      </c>
+      <c r="W28" s="14" t="n">
+        <v>62.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z28" s="3" t="n"/>
+        <v>14.6</v>
+      </c>
+      <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2801,74 +2720,72 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="11" t="n">
-        <v>32.7</v>
+        <v>30.2</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>15.9</v>
+        <v>18.5</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>16.8</v>
+        <v>11.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>91.8</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>682.5</v>
-      </c>
-      <c r="N29" s="8" t="n">
-        <v>92.8</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="n">
-        <v>2</v>
+        <v>90.2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.7</v>
+        <v>22.4</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S29" s="3" t="n">
-        <v>6.4</v>
+      <c r="S29" s="14" t="n">
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>12.4</v>
+        <v>20.8</v>
+      </c>
+      <c r="V29" s="14" t="n">
+        <v>39.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="14" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z29" s="3" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2882,74 +2799,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="16" t="n">
-        <v>306.1</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>4.3</v>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="11" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>119</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.2</v>
+        <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>111.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.5</v>
+        <v>31.3</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>18.5</v>
+        <v>292.7</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>3908.6</v>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>2.4</v>
+        <v>41.2</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>12.7</v>
+        <v>120.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>322.2</v>
-      </c>
+        <v>1112.3</v>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>49.2</v>
+        <v>153822.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>134.6</v>
+        <v>16.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1042.6</v>
+        <v>1104.2</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>14.6</v>
+        <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>322.5</v>
+        <v>312.6</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Z30" s="3" t="n"/>
+        <v>928.4</v>
+      </c>
+      <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2963,74 +2876,68 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="16" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>58.2</v>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="11" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10.6</v>
+        <v>2.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>751.1</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>19.4</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>452.6</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>39.7</v>
+        <v>91.2</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R31" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="R31" s="14" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="T31" s="3" t="n">
-        <v>48.2</v>
+        <v>64.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>2.9</v>
+        <v>20.8</v>
+      </c>
+      <c r="W31" s="14" t="n">
+        <v>22.9</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.3</v>
+        <v>17.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="Z31" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3044,74 +2951,70 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F32" s="15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.8</v>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I32" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="n">
+        <v>1219.6</v>
+      </c>
+      <c r="P32" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>82.90000000000001</v>
+      <c r="Q32" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>2.6</v>
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>23.6</v>
+        <v>22.4</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>2.2</v>
+        <v>22.9</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>0.9</v>
+        <v>25.3</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+        <v>84.5</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3125,42 +3028,38 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>48.41</v>
-      </c>
-      <c r="F33" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>1.5</v>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>14.6</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>5.6</v>
+        <v>94.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>1.2</v>
+        <v>90.2</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3169,30 +3068,30 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>2.3</v>
+        <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.2</v>
+        <v>15</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>28.2</v>
+        <v>24.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>27.4</v>
+      </c>
+      <c r="X33" s="14" t="n">
+        <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+        <v>168.8</v>
+      </c>
+      <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3206,51 +3105,39 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="n">
-        <v>3.6</v>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="16" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>5.3</v>
+        <v>19.4</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>41.8</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>14.6</v>
+        <v>12.7</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.2</v>
+        <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>21.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.5</v>
+        <v>93.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.9</v>
+        <v>12.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>19.7</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="14" t="n">
+        <v>282.5</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>24.8</v>
@@ -3259,27 +3146,27 @@
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>29.6</v>
+        <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>63.2</v>
+        <v>98</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X34" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="X34" s="14" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z34" s="3" t="n"/>
+        <v>16.9</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3293,70 +3180,70 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>25.8</v>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="11" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>27.4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.7</v>
+        <v>18</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N35" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="n">
         <v>92.2</v>
       </c>
-      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R35" s="3" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="S35" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>4</v>
+        <v>19.2</v>
+      </c>
+      <c r="U35" s="14" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V35" s="14" t="n">
+        <v>32</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>6.8</v>
+        <v>24.2</v>
+      </c>
+      <c r="X35" s="14" t="n">
+        <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+        <v>13.2</v>
+      </c>
+      <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3370,78 +3257,70 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F36" s="15" t="n">
-        <v>2.9</v>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="11" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>21.3</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>18.2</v>
+        <v>15.6</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>51.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.9</v>
+        <v>91.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.6</v>
+        <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>31.2</v>
+        <v>1.8</v>
+      </c>
+      <c r="Q36" s="14" t="n">
+        <v>231.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S36" s="8" t="n">
-        <v>97.3</v>
+        <v>23</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U36" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.9</v>
+        <v>23.9</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>58.2</v>
+        <v>27</v>
+      </c>
+      <c r="X36" s="14" t="n">
+        <v>85.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+        <v>11.5</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3455,74 +3334,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="16" t="n">
-        <v>235.6</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>25.8</v>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="18" t="n">
+        <v>1161.5</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>5.6</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4.5</v>
+        <v>8711</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3.9</v>
+        <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1.3</v>
+        <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1.5</v>
+        <v>42.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.7</v>
+        <v>981.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>9450.299999999999</v>
-      </c>
+        <v>941</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>90.2</v>
+        <v>950.6</v>
       </c>
       <c r="P37" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
-      <c r="Q37" s="3" t="n">
-        <v>12.2</v>
-      </c>
       <c r="R37" s="3" t="n">
-        <v>2.4</v>
+        <v>111</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>48.8</v>
+        <v>241.3</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>90.3</v>
+        <v>100.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>1242.1</v>
+        <v>124.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>125.2</v>
+        <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>267.2</v>
+        <v>367.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+        <v>37.2</v>
+      </c>
+      <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3536,72 +3413,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="15" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>22.8</v>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="16" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>18.4</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>26.3</v>
+        <v>51.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>9.4</v>
+        <v>19.9</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>81</v>
+        <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.1</v>
+        <v>21.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>94.09999999999999</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>90.2</v>
+        <v>41</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.6</v>
+        <v>91.2</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>25.8</v>
+        <v>28.6</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>2.6</v>
+        <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.2</v>
+        <v>26.9</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>85.2</v>
+        <v>14.2</v>
+      </c>
+      <c r="U38" s="14" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="V38" s="14" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>0.8</v>
+        <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Z38" s="3" t="n"/>
+      <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3615,72 +3490,72 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="15" t="n">
-        <v>2.3</v>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="14" t="n">
+        <v>32.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="G39" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>245.16</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J39" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="K39" s="3" t="n">
-        <v>1.2</v>
+        <v>61.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O39" s="3" t="n"/>
+      <c r="M39" s="14" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="P39" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>18.6</v>
+        <v>26.4</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>6.2</v>
+        <v>1948.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>28.6</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>20.2</v>
+        <v>82</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>21.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z39" s="3" t="n"/>
+        <v>114.4</v>
+      </c>
+      <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3694,74 +3569,72 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G40" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H40" s="3" t="n">
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="K40" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="L40" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="O40" s="3" t="n"/>
+        <v>42.1</v>
+      </c>
+      <c r="M40" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="n">
+        <v>92.3</v>
+      </c>
       <c r="P40" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>18.2</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q40" s="14" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="R40" s="14" t="n">
+        <v>22.8</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>26.2</v>
+        <v>27</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>47.8</v>
+        <v>39.8</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>2.9</v>
+        <v>28.6</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>2.9</v>
+        <v>25.9</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>7.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z40" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="Z40" s="3" t="inlineStr"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3775,76 +3648,72 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v>42.2</v>
-      </c>
+      <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="11" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G41" s="11" t="n">
-        <v>14.2</v>
+        <v>25.6</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.9</v>
+        <v>21</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5</v>
+        <v>28.6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>18.9</v>
+        <v>15.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>0.1</v>
+        <v>92.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>2.8</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="14" t="n">
+        <v>82</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>4</v>
+        <v>24.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>2.6</v>
+        <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>25.1</v>
+        <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z41" s="3" t="n"/>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3858,74 +3727,70 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="11" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>25.9</v>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="16" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>10.2</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>7</v>
+        <v>54.4</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>62.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.3</v>
+        <v>9.9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>19.3</v>
+        <v>28.8</v>
+      </c>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="14" t="n">
+        <v>11.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>0.1</v>
+        <v>266.2</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>4.1</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
       <c r="R42" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24.6</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="S42" s="14" t="n">
+        <v>49.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>72</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>82.2</v>
+        <v>96.3</v>
+      </c>
+      <c r="V42" s="14" t="n">
+        <v>222.1</v>
+      </c>
+      <c r="W42" s="14" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="X42" s="14" t="n">
+        <v>271.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+        <v>216.7</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3939,84 +3804,30 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="11" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-745
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225778
-22
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-6
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4030,81 +3841,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4262
-7
-</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F44" s="15" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-14
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-7
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77 777
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="T44" s="3" t="n"/>
-      <c r="U44" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X44" s="8" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4118,68 +3878,68 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="16" t="n">
-        <v>122.3</v>
-      </c>
-      <c r="E45" s="16" t="n">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="11" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E45" s="11" t="n">
         <v>18.7</v>
       </c>
-      <c r="F45" s="16" t="n">
-        <v>192.9</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>3.7</v>
+      <c r="F45" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>13.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>69.8</v>
+        <v>117.5</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>282.8</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>18.4</v>
-      </c>
+        <v>190.9</v>
+      </c>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
       <c r="M45" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41272728
-1 8
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n"/>
+        <v>19.9</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P45" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q45" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="3" t="n">
-        <v>5.7</v>
+        <v>22.9</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T45" s="3" t="n"/>
+        <v>160.5</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>9.9</v>
+      </c>
       <c r="U45" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
+        <v>22.8</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>24.2</v>
+      </c>
       <c r="X45" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="Y45" s="3" t="n"/>
-      <c r="Z45" s="3" t="n"/>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4193,67 +3953,38 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 191
-</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F46" s="16" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-278
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n"/>
-      <c r="S46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="8" t="n">
-        <v>290.1</v>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D46" s="13" t="inlineStr"/>
+      <c r="E46" s="13" t="inlineStr"/>
+      <c r="F46" s="13" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="14" t="n">
+        <v>211</v>
+      </c>
+      <c r="X46" s="14" t="n">
+        <v>9885.5</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>116560.8</v>
+      </c>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,20 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +146,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,19 +161,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -796,54 +787,56 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="11" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G4" s="11" t="n">
+      <c r="D4" s="12" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E4" s="12" t="n">
         <v>14.8</v>
       </c>
+      <c r="F4" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="H4" s="3" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="14" t="n">
-        <v>82.90000000000001</v>
+      <c r="J4" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12.4</v>
+        <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>32.6</v>
+        <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>29.3</v>
+        <v>2.9</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>545.2</v>
+        <v>45.2</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
@@ -871,23 +864,23 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>18.8</v>
+      <c r="D5" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>21.3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>81.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.6</v>
+        <v>18.6</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>2.8</v>
@@ -896,46 +889,46 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M5" s="14" t="n">
         <v>17.6</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>31.4</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>29.8</v>
+        <v>20.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X5" s="14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X5" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>76.2</v>
+        <v>16.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -954,40 +947,44 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="11" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>27.7</v>
+      <c r="D6" s="12" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>15.2</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="J6" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M6" s="14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N6" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O6" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
@@ -999,16 +996,16 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>207.4</v>
-      </c>
-      <c r="U6" s="14" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W6" s="14" t="n">
-        <v>51.3</v>
+        <v>2.7</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>41.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
@@ -1017,7 +1014,7 @@
         <v>77.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1033,20 +1030,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>25.2</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>17.8</v>
+      <c r="H7" s="8" t="n">
+        <v>79.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1057,16 +1054,18 @@
       <c r="K7" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="L7" s="14" t="n">
+      <c r="L7" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
       <c r="P7" s="3" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>20.1</v>
@@ -1075,27 +1074,27 @@
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>22.9</v>
+        <v>24.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>81.2</v>
+      </c>
+      <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="X7" s="14" t="n">
-        <v>22.8</v>
+      <c r="X7" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="n">
+        <v>114.8</v>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1110,29 +1109,29 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>14.4</v>
+        <v>1.4</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>18.9</v>
@@ -1142,15 +1141,15 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>9.1</v>
+        <v>91.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="14" t="n">
+      <c r="R8" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1162,8 +1161,8 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="14" t="n">
-        <v>94.59999999999999</v>
+      <c r="V8" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>21.4</v>
@@ -1172,9 +1171,11 @@
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>7.3</v>
       </c>
-      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1189,29 +1190,29 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="11" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>57.8</v>
+      <c r="D9" s="12" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>51.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>957.8</v>
+        <v>5.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
+        <v>1.6</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>949.2</v>
+        <v>47.1</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>92.59999999999999</v>
@@ -1219,9 +1220,11 @@
       <c r="M9" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>100.1</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>1454.6</v>
+        <v>451.6</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1230,26 +1233,28 @@
         <v>129.4</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1110.9</v>
+        <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>142.5</v>
+        <v>126</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1948.8</v>
+        <v>48</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>123.8</v>
+        <v>129.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="X9" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>231.1</v>
+        <v>31.4</v>
       </c>
       <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1266,38 +1271,42 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="D10" s="12" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>97.2</v>
+      <c r="J10" s="8" t="n">
+        <v>860.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="O10" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>25.9</v>
@@ -1309,25 +1318,25 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>164.2</v>
+        <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="14" t="n">
-        <v>282.2</v>
+      <c r="W10" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>25.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>216.2</v>
+        <v>2.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>16.8</v>
+        <v>6.9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1343,67 +1352,71 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G11" s="11" t="n">
+      <c r="E11" s="12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G11" s="12" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
+        <v>13.6</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="K11" s="3" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="L11" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L11" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="M11" s="8" t="n">
+        <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>21.6</v>
+      </c>
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S11" s="14" t="n">
-        <v>26.7</v>
+        <v>28.4</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>65.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>161.2</v>
+        <v>61.2</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
+        <v>14.8</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X11" s="14" t="n">
-        <v>26.8</v>
+        <v>22.7</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>181.2</v>
+        <v>81.2</v>
       </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1419,56 +1432,62 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="11" t="n">
+      <c r="C12" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>26.5</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.9</v>
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.5</v>
+        <v>81.5</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L12" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="8" t="n">
+        <v>22.6</v>
+      </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.9</v>
+        <v>2.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>161.2</v>
+        <v>67.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
@@ -1480,9 +1499,11 @@
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="Z12" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>164.5</v>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1497,44 +1518,50 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>22.7</v>
+      <c r="E13" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>2.2</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="14" t="n">
-        <v>19.9</v>
+        <v>12.6</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>19.2</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>15.8</v>
+        <v>25.3</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>46.4</v>
+        <v>20.4</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>22.9</v>
@@ -1543,7 +1570,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1551,13 +1578,15 @@
       <c r="W13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X13" s="14" t="n">
+      <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>185.2</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+        <v>85.2</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2.3</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1571,20 +1600,22 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="11" t="n">
+      <c r="C14" s="3" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="H14" s="14" t="n">
+      <c r="E14" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H14" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1594,38 +1625,40 @@
         <v>20.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M14" s="14" t="n">
-        <v>341.4</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="O14" s="3" t="n">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q14" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="R14" s="14" t="n">
-        <v>923.4</v>
+      <c r="R14" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.8</v>
+        <v>2.5</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58.2</v>
+        <v>5.8</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V14" s="14" t="n">
-        <v>25.2</v>
+      <c r="V14" s="8" t="n">
+        <v>15.1</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>22.8</v>
@@ -1634,9 +1667,11 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="Z14" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>951.4</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1651,69 +1686,75 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="11" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>23.8</v>
+      <c r="D15" s="16" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>16.8</v>
+        <v>2.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>12.1</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>91</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>26.6</v>
+        <v>2.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>25.7</v>
+        <v>4.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>38.2</v>
+        <v>58.2</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>9.5</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>85.3</v>
+        <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Z15" s="3" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1728,69 +1769,69 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <v>140.8</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <v>92.3</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4</v>
+        <v>48.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>18.8</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
+        <v>14.3</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="L16" s="3" t="n">
-        <v>2.1</v>
+        <v>951.3</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>453.2</v>
+        <v>9455.200000000001</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>4.5</v>
+        <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>12.2</v>
+        <v>16.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1182.3</v>
+        <v>1182.9</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>118.8</v>
+        <v>21314.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1949.2</v>
+        <v>99.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>10.1</v>
+        <v>1158.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1124.6</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>1708.8</v>
-      </c>
+        <v>11274.6</v>
+      </c>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>1151</v>
+        <v>100.5</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1806,48 +1847,54 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="11" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="C17" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G17" s="12" t="n">
         <v>9.6</v>
       </c>
-      <c r="H17" s="14" t="n">
-        <v>12.9</v>
+      <c r="H17" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M17" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>191.2</v>
+        <v>9.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>25.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>51.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>22.5</v>
+        <v>28.5</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>25.3</v>
+        <v>23.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>64.90000000000001</v>
@@ -1856,11 +1903,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
+        <v>222.3</v>
+      </c>
+      <c r="W17" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
       <c r="X17" s="3" t="n">
-        <v>82.2</v>
+        <v>24.8</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>2</v>
@@ -1880,11 +1929,11 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="n">
-        <v>30.2</v>
+      <c r="D18" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>24.9</v>
@@ -1893,51 +1942,53 @@
         <v>12.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>46.6</v>
+        <v>12.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M18" s="14" t="n">
-        <v>11</v>
+        <v>19.8</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>228.8</v>
-      </c>
-      <c r="P18" s="14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Q18" s="3" t="inlineStr"/>
+        <v>91.2</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="R18" s="3" t="n">
-        <v>2.4</v>
+        <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>94.2</v>
+        <v>54.8</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>85.2</v>
+        <v>24.3</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>1</v>
@@ -1957,51 +2008,57 @@
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <v>30.6</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>17.6</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>24.1</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="12" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
+        <v>27.9</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>418.3</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P19" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="14" t="n">
+      <c r="R19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>23</v>
+        <v>2.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>10.2</v>
+        <v>18.8</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
@@ -2009,11 +2066,11 @@
       <c r="W19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="X19" s="14" t="n">
-        <v>21.8</v>
+      <c r="X19" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2029,42 +2086,48 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E20" s="3" t="n">
+      <c r="C20" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E20" s="12" t="n">
         <v>18.9</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>19.6</v>
+      <c r="G20" s="12" t="n">
+        <v>9.6</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>48.6</v>
+        <v>17.6</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="n">
+        <v>90.2</v>
+      </c>
       <c r="P20" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>26.2</v>
+        <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.9</v>
@@ -2073,22 +2136,22 @@
         <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>12.2</v>
+        <v>82.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="14" t="n">
-        <v>82.8</v>
+        <v>10.9</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>41.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2105,20 +2168,20 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="11" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>1.3</v>
+      <c r="D21" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>17.3</v>
+        <v>1.4</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2127,45 +2190,45 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>73.8</v>
+        <v>7.8</v>
       </c>
       <c r="L21" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>13.4</v>
-      </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="14" t="n">
-        <v>19.1</v>
+      <c r="R21" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>19.1</v>
+        <v>13.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>90.2</v>
-      </c>
+      <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2182,69 +2245,71 @@
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>23.5</v>
+      <c r="D22" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.9</v>
+        <v>1.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="14" t="n">
+      <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>10.8</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>91.2</v>
+        <v>99.2</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="14" t="n">
-        <v>39.9</v>
+      <c r="R22" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>956.2</v>
-      </c>
-      <c r="U22" s="14" t="n">
-        <v>39.9</v>
+        <v>856.2</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="V22" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W22" s="3" t="n">
         <v>22.6</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>26.8</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>80.2</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>194.7</v>
+        <v>94.7</v>
       </c>
       <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
@@ -2260,63 +2325,69 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="18" t="n">
-        <v>1144.1</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>290.4</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>1944.6</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>910.4</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>57.2</v>
+      </c>
       <c r="H23" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+        <v>220.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>72.5</v>
+      </c>
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2464.4</v>
+        <v>21.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.1</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1420.9</v>
+        <v>22.9</v>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>931.6</v>
+        <v>931.2</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1121</v>
+        <v>121</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>4.8</v>
+        <v>11.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>9360.6</v>
+        <v>96</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>1108.4</v>
+        <v>47.9</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>102.6</v>
+        <v>108.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.7</v>
+        <v>197.4</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>927.8</v>
+        <v>118.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>12.4</v>
@@ -2336,61 +2407,63 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="18" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>829.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>11.4</v>
+      <c r="D24" s="17" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr"/>
+        <v>11.9</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>58.9</v>
+      </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>98.8</v>
       </c>
-      <c r="M24" s="14" t="n">
-        <v>316.4</v>
+      <c r="M24" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="n">
+        <v>531.2</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="S24" s="14" t="n">
-        <v>23.9</v>
+        <v>21.4</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>728.2</v>
+        <v>12.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="8" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="W24" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>85.2</v>
-      </c>
+      <c r="X24" s="3" t="inlineStr"/>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
@@ -2409,69 +2482,69 @@
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="11" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G25" s="11" t="n">
+      <c r="D25" s="12" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15.2</v>
+        <v>11.2</v>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>1192.2</v>
-      </c>
-      <c r="P25" s="14" t="n">
-        <v>9</v>
+        <v>15.5</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>11.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>25.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X25" s="14" t="n">
-        <v>69.2</v>
+        <v>29.9</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>67.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>9.1</v>
+        <v>59.1</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2488,13 +2561,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="11" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F26" s="11" t="n">
+      <c r="D26" s="12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2509,31 +2582,35 @@
       <c r="J26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K26" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>71.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>91.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>27.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.1</v>
+        <v>47.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>716.2</v>
+        <v>26.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2544,7 +2621,7 @@
       <c r="W26" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="X26" s="14" t="n">
+      <c r="X26" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y26" s="3" t="n">
@@ -2564,21 +2641,23 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="11" t="n">
+      <c r="C27" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>27.3</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="12" t="n">
         <v>17.5</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="12" t="n">
         <v>22.4</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="G27" s="12" t="n">
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>1.5</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
@@ -2587,17 +2666,19 @@
         <v>9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
+        <v>91.2</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O27" s="3" t="n">
-        <v>49.4</v>
+        <v>4.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
@@ -2606,26 +2687,26 @@
         <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="U27" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="U27" s="3" t="inlineStr"/>
-      <c r="V27" s="14" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X27" s="14" t="n">
+      <c r="V27" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
         <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2642,69 +2723,71 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="11" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="D28" s="12" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="14" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H28" s="14" t="n">
+      <c r="G28" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="M28" s="14" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>21.1</v>
+      </c>
       <c r="O28" s="3" t="n">
-        <v>119080.9</v>
+        <v>122.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>25.6</v>
+        <v>2.3</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>74</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W28" s="14" t="n">
-        <v>62.2</v>
+        <v>21.8</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>61.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.6</v>
+        <v>17.6</v>
       </c>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2721,42 +2804,44 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="11" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F29" s="11" t="n">
+      <c r="D29" s="12" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>24.2</v>
       </c>
-      <c r="G29" s="11" t="n">
-        <v>11.2</v>
+      <c r="G29" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J29" s="14" t="n">
-        <v>91.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="14" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="M29" s="14" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>90.2</v>
+        <v>40.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>22.4</v>
@@ -2764,26 +2849,26 @@
       <c r="R29" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S29" s="14" t="n">
+      <c r="S29" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="V29" s="14" t="n">
-        <v>39.4</v>
+        <v>2.5</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X29" s="14" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="X29" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2799,15 +2884,17 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="11" t="n">
-        <v>168.5</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>119</v>
+      <c r="C30" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>94</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>58.8</v>
@@ -2816,51 +2903,53 @@
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>31.3</v>
+        <v>4.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>292.7</v>
+        <v>12.4</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>16.4</v>
+        <v>18.6</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>41.2</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>120.7</v>
+        <v>920.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1112.3</v>
-      </c>
-      <c r="S30" s="3" t="inlineStr"/>
+        <v>112.9</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>126.4</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>153822.2</v>
+        <v>3322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.1</v>
+        <v>1088.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1104.2</v>
+        <v>1184.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>114.6</v>
+        <v>115.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>312.6</v>
+        <v>108.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>928.4</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2877,65 +2966,69 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="11" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G31" s="11" t="n">
-        <v>19.8</v>
+      <c r="D31" s="12" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="M31" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>25.9</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="R31" s="14" t="n">
-        <v>82.59999999999999</v>
+        <v>26.3</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>25.3</v>
+        <v>2.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>23.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="W31" s="14" t="n">
-        <v>22.9</v>
+        <v>25.6</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>17.3</v>
+        <v>77.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>6.5</v>
+        <v>14.1</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -2952,26 +3045,26 @@
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="11" t="n">
-        <v>32.8</v>
+      <c r="D32" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
@@ -2982,9 +3075,11 @@
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>1219.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
@@ -2993,25 +3088,25 @@
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>22.4</v>
+        <v>288.1</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="inlineStr"/>
@@ -3028,38 +3123,44 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="11" t="n">
+      <c r="C33" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D33" s="12" t="n">
         <v>32.6</v>
       </c>
-      <c r="E33" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>14.6</v>
+      <c r="E33" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>94.5</v>
+        <v>4.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>90.2</v>
+        <v>59.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3074,22 +3175,22 @@
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U33" s="3" t="n">
-        <v>24.2</v>
-      </c>
       <c r="V33" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="X33" s="14" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X33" s="3" t="n">
         <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>168.8</v>
+        <v>165.8</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3105,42 +3206,50 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="16" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="G34" s="3" t="n">
+      <c r="C34" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G34" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>93.5</v>
+        <v>13.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
-      <c r="O34" s="3" t="inlineStr"/>
-      <c r="P34" s="14" t="n">
-        <v>282.5</v>
+      <c r="M34" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3149,22 +3258,22 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98</v>
+        <v>68.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="X34" s="14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="X34" s="3" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>16.9</v>
+        <v>6.2</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3181,20 +3290,20 @@
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="11" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>27.4</v>
+      <c r="D35" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>0.8</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.2</v>
+        <v>10.2</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>1.9</v>
@@ -3208,10 +3317,14 @@
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>30.1</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>92.2</v>
+        <v>994.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3226,22 +3339,22 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="U35" s="14" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V35" s="14" t="n">
-        <v>32</v>
+        <v>12.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="X35" s="14" t="n">
+      <c r="X35" s="3" t="n">
         <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>13.2</v>
+        <v>113.2</v>
       </c>
       <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3258,26 +3371,26 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G36" s="3" t="n">
+      <c r="D36" s="12" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G36" s="12" t="n">
         <v>15.6</v>
       </c>
-      <c r="H36" s="14" t="n">
-        <v>51.4</v>
+      <c r="H36" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>91.8</v>
+        <v>0.5</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
@@ -3286,18 +3399,20 @@
         <v>18.9</v>
       </c>
       <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>9</v>
+        <v>470.6</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q36" s="14" t="n">
-        <v>231.2</v>
+        <v>1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>31.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
@@ -3306,7 +3421,7 @@
         <v>12.6</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>28.3</v>
+        <v>2.8</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>23.9</v>
@@ -3314,11 +3429,11 @@
       <c r="W36" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="X36" s="14" t="n">
-        <v>85.2</v>
+      <c r="X36" s="3" t="n">
+        <v>55.7</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3335,20 +3450,20 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="18" t="n">
+      <c r="D37" s="17" t="n">
         <v>1161.5</v>
       </c>
-      <c r="E37" s="18" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="F37" s="18" t="n">
+      <c r="E37" s="17" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="F37" s="17" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8711</v>
+        <v>818</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
@@ -3357,47 +3472,49 @@
         <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>42.2</v>
+        <v>49.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>981.1</v>
+        <v>28.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>941</v>
-      </c>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>721</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="O37" s="3" t="n">
         <v>950.6</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>2.6</v>
+        <v>120.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="V37" s="3" t="n">
         <v>111</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>241.3</v>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>124.8</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>116</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>367.2</v>
+        <v>3672.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>37.2</v>
+        <v>537.2</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3414,40 +3531,42 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="16" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="E38" s="18" t="n">
+      <c r="D38" s="17" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E38" s="17" t="n">
         <v>18.4</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>51.5</v>
+        <v>524.6</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>21.3</v>
+        <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>0.1</v>
+        <v>14.4</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>41</v>
+        <v>50.7</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>91.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>28.6</v>
@@ -3456,16 +3575,16 @@
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.9</v>
+        <v>28.9</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U38" s="14" t="n">
-        <v>274.9</v>
-      </c>
-      <c r="V38" s="14" t="n">
-        <v>22.2</v>
+        <v>14.9</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>82.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
@@ -3474,7 +3593,7 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3491,39 +3610,39 @@
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="14" t="n">
-        <v>32.6</v>
+      <c r="D39" s="3" t="n">
+        <v>32.2</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.5</v>
+        <v>10.2</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>245.16</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="H39" s="14" t="n">
-        <v>11</v>
+        <v>35.6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M39" s="14" t="n">
-        <v>19.8</v>
+        <v>68.2</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>11.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3531,17 +3650,17 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>22.6</v>
+      <c r="R39" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>1948.2</v>
+        <v>61.6</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>28.6</v>
+        <v>21.8</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>82</v>
@@ -3550,11 +3669,9 @@
         <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>114.4</v>
-      </c>
+        <v>21.6</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3570,66 +3687,68 @@
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="F40" s="3" t="n">
+      <c r="D40" s="12" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>25.4</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H40" s="14" t="n">
-        <v>18.8</v>
+      <c r="G40" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="J40" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J40" s="3" t="n">
         <v>91</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="M40" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="N40" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="14" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="R40" s="14" t="n">
+      <c r="Q40" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="U40" s="3" t="n">
         <v>22.8</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>9</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>25.9</v>
+      <c r="W40" s="8" t="n">
+        <v>51.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
@@ -3649,54 +3768,54 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="11" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G41" s="3" t="n">
+      <c r="D41" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G41" s="12" t="n">
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21</v>
+        <v>2.9</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>28.6</v>
+        <v>4.1</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>15.4</v>
+        <v>10</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>4.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>92.2</v>
+        <v>91.2</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="R41" s="14" t="n">
-        <v>82</v>
+        <v>2.4</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>24.6</v>
+        <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>91</v>
+        <v>11.8</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>22.8</v>
@@ -3705,10 +3824,10 @@
         <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3728,68 +3847,62 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="16" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>10.2</v>
+      <c r="D42" s="12" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="H42" s="14" t="n">
-        <v>62.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9.9</v>
+        <v>2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>15.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="14" t="n">
-        <v>11.9</v>
+        <v>1.5</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>950.2</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>29.2</v>
+        <v>11.8</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>266.2</v>
+        <v>92.2</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q42" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="R42" s="3" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="S42" s="14" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="V42" s="14" t="n">
-        <v>222.1</v>
-      </c>
-      <c r="W42" s="14" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="X42" s="14" t="n">
-        <v>271.2</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>216.7</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="3" t="inlineStr"/>
+      <c r="W42" s="3" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3804,10 +3917,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
-      <c r="F43" s="12" t="inlineStr"/>
+      <c r="C43" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D43" s="11" t="inlineStr"/>
+      <c r="E43" s="11" t="inlineStr"/>
+      <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
@@ -3841,10 +3956,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="12" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="11" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3879,65 +3996,69 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="11" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G45" s="11" t="n">
-        <v>13.7</v>
+      <c r="D45" s="17" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>182</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>117.5</v>
+        <v>62.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>9.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>190.9</v>
-      </c>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>14.1</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>19.9</v>
+        <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>22.3</v>
+        <v>89</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>92.2</v>
+        <v>266.6</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="3" t="n">
-        <v>22.9</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>160.5</v>
+        <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>9.9</v>
+        <v>509.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>22.8</v>
+        <v>96.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21.8</v>
+        <v>818.7</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>24.2</v>
+        <v>966.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>271.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>51.8</v>
+        <v>5.8</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -3953,36 +4074,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D46" s="13" t="inlineStr"/>
-      <c r="E46" s="13" t="inlineStr"/>
-      <c r="F46" s="13" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="12" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
-      <c r="P46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="n">
+        <v>22.9</v>
+      </c>
       <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="14" t="n">
-        <v>211</v>
-      </c>
-      <c r="X46" s="14" t="n">
-        <v>9885.5</v>
+      <c r="T46" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>82.2</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>116560.8</v>
+        <v>1211101.1</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -41,26 +41,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,22 +149,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -787,20 +778,20 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="12" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E4" s="12" t="n">
+      <c r="D4" s="11" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G4" s="11" t="n">
         <v>14.8</v>
       </c>
-      <c r="F4" s="12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>14.8</v>
-      </c>
       <c r="H4" s="3" t="n">
-        <v>15.9</v>
+        <v>15.3</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
@@ -818,10 +809,10 @@
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>21.9</v>
+        <v>8.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>91.8</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -833,7 +824,7 @@
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.9</v>
+        <v>25.2</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>45.2</v>
@@ -842,7 +833,7 @@
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>21.5</v>
+        <v>27.5</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
@@ -863,42 +854,44 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="12" t="n">
+      <c r="C5" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>21.3</v>
+      <c r="F5" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>18.6</v>
+        <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>14.6</v>
+      <c r="M5" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.8</v>
+        <v>2</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
@@ -910,19 +903,19 @@
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.1</v>
+        <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="W5" s="8" t="n">
-        <v>21.8</v>
+        <v>43.9</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>29.9</v>
@@ -947,17 +940,17 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="12" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="F6" s="12" t="n">
+      <c r="D6" s="3" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.5</v>
+        <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>14.4</v>
@@ -966,25 +959,25 @@
         <v>2.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>15.4</v>
+        <v>17.4</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>97.5</v>
+        <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>81.2</v>
+        <v>91.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
@@ -996,22 +989,22 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>2.7</v>
+        <v>27.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>41.3</v>
+        <v>21.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>77.2</v>
+        <v>17.8</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1030,16 +1023,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="11" t="n">
         <v>10.6</v>
       </c>
       <c r="H7" s="8" t="n">
@@ -1065,35 +1058,37 @@
         <v>90.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>24.2</v>
+        <v>2.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="U7" s="3" t="inlineStr"/>
+        <v>87.2</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>114.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1108,27 +1103,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="12" t="n">
+      <c r="C8" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="11" t="n">
         <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.4</v>
@@ -1156,13 +1153,13 @@
         <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>66.2</v>
+        <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>24.6</v>
+        <v>2.4</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>21.4</v>
@@ -1171,10 +1168,10 @@
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>59.2</v>
+        <v>69.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1190,17 +1187,17 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="12" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>117.5</v>
+      <c r="D9" s="11" t="n">
+        <v>147.4</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>51.8</v>
+        <v>54.8</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>5.7</v>
@@ -1209,13 +1206,13 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.6</v>
+        <v>16.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>47.1</v>
+        <v>944.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>92.59999999999999</v>
@@ -1224,7 +1221,7 @@
         <v>100.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>451.6</v>
+        <v>452.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1236,16 +1233,16 @@
         <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>129.8</v>
+        <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>11</v>
@@ -1254,7 +1251,7 @@
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1270,29 +1267,33 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="12" t="n">
+      <c r="C10" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>29.5</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>23.5</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>19.6</v>
+      <c r="G10" s="8" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>860.4</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>18.5</v>
       </c>
@@ -1300,7 +1301,7 @@
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>91.2</v>
@@ -1321,7 +1322,7 @@
         <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>24.8</v>
@@ -1336,7 +1337,7 @@
         <v>2.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1352,68 +1353,66 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>13.6</v>
+        <v>1.8</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="M11" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>21.6</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>65.7</v>
+      <c r="R11" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>61.2</v>
+        <v>6.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>14.8</v>
+        <v>24.8</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>16.8</v>
+        <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>81.2</v>
@@ -1433,22 +1432,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D12" s="12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.1</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>81.5</v>
+        <v>17.3</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>1.6</v>
@@ -1457,7 +1456,7 @@
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>19</v>
@@ -1465,7 +1464,7 @@
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O12" s="3" t="n">
@@ -1475,34 +1474,34 @@
         <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>25.8</v>
+        <v>2.5</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>67.2</v>
+        <v>61.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>164.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1524,20 +1523,20 @@
       <c r="E13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="F13" s="16" t="n">
-        <v>2.2</v>
+      <c r="F13" s="3" t="n">
+        <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>8.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12.6</v>
+        <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>27.5</v>
+        <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8</v>
@@ -1549,7 +1548,7 @@
         <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>25.3</v>
+        <v>24.3</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1558,7 +1557,7 @@
         <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>20.4</v>
@@ -1570,7 +1569,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1600,22 +1599,20 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>133.1</v>
-      </c>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>14.2</v>
+      <c r="E14" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>24.1</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1631,28 +1628,26 @@
         <v>18.9</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
+        <v>19.7</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>21.4</v>
+        <v>31.4</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>5.8</v>
+        <v>88.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
@@ -1667,10 +1662,10 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>17.2</v>
+        <v>717.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>951.4</v>
+        <v>51.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1685,45 +1680,47 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="16" t="n">
-        <v>39.19</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="C15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G15" s="11" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>12.1</v>
+        <v>29.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>2.6</v>
@@ -1731,8 +1728,8 @@
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="3" t="n">
-        <v>4.8</v>
+      <c r="S15" s="8" t="n">
+        <v>22.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1743,8 +1740,8 @@
       <c r="V15" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>9.5</v>
+      <c r="W15" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.4</v>
@@ -1753,7 +1750,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1769,29 +1766,29 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="12" t="n">
-        <v>140.8</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>116.6</v>
+      <c r="D16" s="13" t="n">
+        <v>1940.4</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>114.6</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>48.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
+        <v>17.3</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>951.3</v>
@@ -1803,35 +1800,35 @@
         <v>10.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>9455.200000000001</v>
+        <v>453.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>16.2</v>
+        <v>122.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1182.9</v>
+        <v>1127.3</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>21314.2</v>
+        <v>18.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>99.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1158.5</v>
+        <v>984.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>11274.6</v>
+        <v>1124.6</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>100.5</v>
+        <v>10064.6</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1847,19 +1844,17 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="13" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E17" s="13" t="n">
         <v>19.3</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G17" s="12" t="n">
+      <c r="F17" s="13" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1869,41 +1864,39 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="M17" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>51.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>23.3</v>
+        <v>22.5</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>35.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>222.3</v>
+        <v>22.7</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>21.5</v>
@@ -1929,23 +1922,23 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="8" t="n">
-        <v>8.9</v>
+      <c r="D18" s="3" t="n">
+        <v>30.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12.8</v>
+        <v>18.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>24.9</v>
+        <v>25.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12.9</v>
+        <v>1.2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>2.6</v>
@@ -1954,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
@@ -1967,7 +1960,7 @@
         <v>0.2</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>2.1</v>
+        <v>29.2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.2</v>
@@ -1976,16 +1969,16 @@
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>54.8</v>
+        <v>94.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
+        <v>10.4</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>24.3</v>
@@ -2007,21 +2000,23 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="12" t="n">
+      <c r="C19" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F19" s="12" t="n">
+      <c r="E19" s="11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F19" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="11" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.5</v>
+        <v>46.9</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.3</v>
@@ -2032,8 +2027,8 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>418.3</v>
+      <c r="L19" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>18.2</v>
@@ -2052,13 +2047,13 @@
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>2.4</v>
+        <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>18.8</v>
+        <v>10.8</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
@@ -2086,19 +2081,17 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F20" s="12" t="n">
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2117,9 +2110,11 @@
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>19.2</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O20" s="3" t="n">
         <v>90.2</v>
       </c>
@@ -2133,22 +2128,22 @@
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>82.2</v>
+        <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>41.8</v>
+        <v>81.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2168,8 +2163,8 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="n">
-        <v>28.7</v>
+      <c r="D21" s="14" t="n">
+        <v>1.5</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2178,10 +2173,10 @@
         <v>21.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1</v>
+        <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2190,7 +2185,7 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>7.8</v>
+        <v>73.8</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>19.4</v>
@@ -2206,19 +2201,19 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>19.2</v>
+        <v>11.2</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>13.5</v>
@@ -2246,25 +2241,25 @@
       </c>
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E22" s="16" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="E22" s="14" t="n">
         <v>1.7</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>23.2</v>
+      <c r="F22" s="8" t="n">
+        <v>32.8</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.2</v>
+        <v>23.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
@@ -2273,10 +2268,10 @@
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>10.8</v>
+        <v>18</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>99.2</v>
@@ -2294,7 +2289,7 @@
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>856.2</v>
+        <v>8956.200000000001</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
@@ -2325,57 +2320,55 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>1944.6</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>910.4</v>
-      </c>
-      <c r="F23" s="17" t="n">
-        <v>112.8</v>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="13" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>119.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>57.2</v>
+        <v>5.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>220.8</v>
+        <v>85.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>72.5</v>
+        <v>2.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>21.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>931.2</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>43.1</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
         <v>121</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>107.2</v>
+        <v>107.9</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>96</v>
+        <v>360.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>47.9</v>
@@ -2384,13 +2377,13 @@
         <v>108.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.4</v>
+        <v>19.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>118.8</v>
+        <v>94927.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr">
@@ -2407,58 +2400,58 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="17" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F24" s="17" t="n">
+      <c r="D24" s="11" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F24" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>91.40000000000001</v>
+      <c r="G24" s="11" t="n">
+        <v>11.4</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>58.9</v>
+        <v>8.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>98.8</v>
+        <v>88.8</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>531.2</v>
+        <v>581.2</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>21</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>823.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>12.2</v>
+        <v>78.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="8" t="n">
-        <v>81.7</v>
+      <c r="V24" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>20.5</v>
@@ -2481,40 +2474,40 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="12" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>-30.5</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+        <v>42.4</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>15.5</v>
+        <v>24.2</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
@@ -2529,22 +2522,22 @@
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>29.9</v>
+        <v>23.1</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>67.8</v>
+        <v>71.3</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>59.1</v>
+        <v>9.1</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2561,20 +2554,20 @@
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.7</v>
+        <v>1.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.2</v>
@@ -2583,34 +2576,32 @@
         <v>1.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>2.3</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>71.8</v>
-      </c>
+        <v>20.6</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>23.9</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>47.9</v>
+        <v>27.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>26.2</v>
+        <v>76.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2641,53 +2632,51 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E27" s="12" t="n">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E27" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="11" t="n">
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>91.2</v>
+        <v>18.8</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>26.6</v>
+        <v>2.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
@@ -2696,9 +2685,9 @@
         <v>63.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V27" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="V27" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W27" s="3" t="inlineStr"/>
@@ -2706,7 +2695,7 @@
         <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2723,44 +2712,44 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="12" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F28" s="12" t="n">
+      <c r="D28" s="11" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F28" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>18.8</v>
+      <c r="G28" s="11" t="n">
+        <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.6</v>
+        <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>21.1</v>
+        <v>0.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>122.2</v>
+        <v>1272.4</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
@@ -2768,26 +2757,26 @@
       <c r="R28" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="S28" s="8" t="n">
-        <v>74</v>
+      <c r="S28" s="3" t="n">
+        <v>27.6</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>61.2</v>
+        <v>24.8</v>
+      </c>
+      <c r="W28" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>17.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2804,23 +2793,23 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="11" t="n">
         <v>30.1</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>1.9</v>
+      <c r="G29" s="11" t="n">
+        <v>11.7</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>9.800000000000001</v>
@@ -2832,13 +2821,11 @@
         <v>19.2</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>4.8</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="n">
-        <v>40.3</v>
+        <v>40.7</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>8</v>
@@ -2849,7 +2836,7 @@
       <c r="R29" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
@@ -2862,13 +2849,13 @@
         <v>20.1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>28.8</v>
+        <v>21.8</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2884,17 +2871,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>148.5</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>94</v>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="11" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>119</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>58.8</v>
@@ -2909,47 +2894,47 @@
         <v>11.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>12.4</v>
+        <v>92.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>18.6</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>920.7</v>
+        <v>130.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>112.9</v>
+        <v>112.7</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>3322.2</v>
+        <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1088.1</v>
+        <v>118.2</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1184.1</v>
+        <v>18.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>115.6</v>
+        <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>108.4</v>
+        <v>374.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2966,14 +2951,14 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="12" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>18.8</v>
+      <c r="D31" s="11" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>23.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>11.9</v>
@@ -2988,35 +2973,35 @@
         <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
-        <v>1</v>
+      <c r="L31" s="8" t="n">
+        <v>10.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>22.5</v>
+      <c r="R31" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.6</v>
@@ -3028,7 +3013,7 @@
         <v>77.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>14.1</v>
+        <v>6.3</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -3046,40 +3031,38 @@
       </c>
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E32" s="16" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E32" s="14" t="n">
         <v>1.8</v>
       </c>
-      <c r="F32" s="16" t="n">
-        <v>2.5</v>
+      <c r="F32" s="3" t="n">
+        <v>25.6</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="H32" s="8" t="n">
-        <v>11.8</v>
+      <c r="H32" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.9</v>
+        <v>29.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
@@ -3088,15 +3071,15 @@
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="U32" s="8" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
@@ -3106,7 +3089,7 @@
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.2</v>
+        <v>84.8</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="inlineStr"/>
@@ -3123,17 +3106,15 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>25.8</v>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>2.5</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>1.4</v>
@@ -3142,7 +3123,7 @@
         <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.5</v>
@@ -3150,17 +3131,15 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N33" s="3" t="n">
+      <c r="M33" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="n">
         <v>10.8</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>59.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3169,28 +3148,28 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.6</v>
+        <v>12.8</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>15</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>20</v>
+        <v>29.2</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>21.4</v>
+        <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>165.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3206,19 +3185,17 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E34" s="12" t="n">
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="11" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E34" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G34" s="11" t="n">
         <v>12.7</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3228,28 +3205,28 @@
         <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>51.1</v>
+      <c r="M34" s="8" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>27.8</v>
+        <v>24.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3258,10 +3235,10 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>68.2</v>
+        <v>69.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3273,7 +3250,7 @@
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3290,20 +3267,20 @@
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="16" t="n">
-        <v>0.4</v>
+      <c r="D35" s="3" t="n">
+        <v>30.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>0.8</v>
+        <v>19.4</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>10.2</v>
+        <v>18.2</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>1.9</v>
@@ -3315,16 +3292,16 @@
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>30.1</v>
+        <v>1.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>994.2</v>
+        <v>172.4</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3339,13 +3316,13 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>12.2</v>
+        <v>192.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.2</v>
@@ -3354,7 +3331,7 @@
         <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>113.2</v>
+        <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3371,26 +3348,26 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="12" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="F36" s="12" t="n">
+      <c r="D36" s="14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F36" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>15.6</v>
+      <c r="G36" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
@@ -3398,12 +3375,12 @@
       <c r="L36" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="M36" s="8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>470.6</v>
+        <v>70.7</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
@@ -3412,13 +3389,13 @@
         <v>31.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>2.8</v>
@@ -3430,10 +3407,10 @@
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>55.7</v>
+        <v>8.5</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3450,71 +3427,71 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="17" t="n">
-        <v>1161.5</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="F37" s="17" t="n">
+      <c r="D37" s="11" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F37" s="11" t="n">
         <v>126.9</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>9.4</v>
+      <c r="G37" s="11" t="n">
+        <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>818</v>
+        <v>81</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>20.3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>49.9</v>
+        <v>949.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>28.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>721</v>
+        <v>92</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>950.6</v>
+        <v>950.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>120.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>120.6</v>
+        <v>1230.4</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>101</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>124.1</v>
+        <v>12.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>3672.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>537.2</v>
+        <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3531,39 +3508,39 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="17" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E38" s="17" t="n">
+      <c r="D38" s="11" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E38" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="16" t="n">
-        <v>524.6</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="H38" s="8" t="n">
+      <c r="F38" s="11" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>14.5</v>
+        <v>9.9</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>7.2</v>
+        <v>46.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>50.7</v>
+        <v>30.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.2</v>
@@ -3575,7 +3552,7 @@
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>28.9</v>
+        <v>28.1</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>14.9</v>
@@ -3584,7 +3561,7 @@
         <v>24.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>82.2</v>
+        <v>22.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
@@ -3593,7 +3570,7 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3614,35 +3591,35 @@
         <v>32.2</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>35.6</v>
+        <v>18.5</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>19</v>
+        <v>17.9</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>81</v>
+        <v>19.9</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>13</v>
+        <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>796</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3650,26 +3627,26 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="R39" s="3" t="n">
         <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>61.6</v>
+        <v>69.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr"/>
@@ -3687,29 +3664,29 @@
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="12" t="n">
+      <c r="D40" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="11" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
@@ -3717,8 +3694,8 @@
       <c r="M40" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>11.8</v>
+      <c r="N40" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3726,17 +3703,17 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S40" s="8" t="n">
-        <v>60.8</v>
+      <c r="Q40" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>192.6</v>
+        <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>22.8</v>
@@ -3744,11 +3721,11 @@
       <c r="V40" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>51.8</v>
+      <c r="W40" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>26.9</v>
+        <v>8.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
@@ -3768,16 +3745,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="F41" s="12" t="n">
+      <c r="D41" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="G41" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3787,24 +3764,22 @@
         <v>2.9</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>4.9</v>
+      <c r="L41" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>99.2</v>
+      </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="3" t="n">
         <v>2.4</v>
       </c>
@@ -3815,19 +3790,19 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>11.8</v>
+        <v>2.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.2</v>
+        <v>2.4</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>2.2</v>
+        <v>68.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3847,39 +3822,37 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="12" t="n">
+      <c r="D42" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F42" s="12" t="n">
+      <c r="E42" s="14" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>950.2</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="L42" s="8" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr"/>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -3892,12 +3865,14 @@
       <c r="R42" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="S42" s="8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="8" t="n">
-        <v>1</v>
+      <c r="S42" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="V42" s="3" t="inlineStr"/>
       <c r="W42" s="3" t="inlineStr"/>
@@ -3920,9 +3895,9 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="11" t="inlineStr"/>
-      <c r="E43" s="11" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
@@ -3959,9 +3934,9 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="11" t="inlineStr"/>
-      <c r="E44" s="11" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3996,41 +3971,41 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="13" t="n">
         <v>122.3</v>
       </c>
-      <c r="E45" s="17" t="n">
+      <c r="E45" s="13" t="n">
         <v>24.6</v>
       </c>
-      <c r="F45" s="17" t="n">
-        <v>182</v>
+      <c r="F45" s="13" t="n">
+        <v>162</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>18.8</v>
+        <v>5.4</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>62.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>9.9</v>
+        <v>0.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>14.1</v>
+        <v>141.1</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>89</v>
+        <v>8.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>266.6</v>
+        <v>26.6</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
@@ -4043,22 +4018,22 @@
         <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>509.7</v>
+        <v>32.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>96.2</v>
+        <v>95.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>818.7</v>
+        <v>22.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>966.3</v>
+        <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>271.2</v>
+        <v>221.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4075,17 +4050,17 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="11" t="n">
         <v>32.3</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="11" t="n">
         <v>18.7</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="F46" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>93.7</v>
+      <c r="G46" s="11" t="n">
+        <v>13.7</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>17.5</v>
@@ -4093,21 +4068,23 @@
       <c r="I46" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="J46" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
-        <v>18.1</v>
+      <c r="J46" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>42.7</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>19.3</v>
+        <v>11.9</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
@@ -4130,10 +4107,10 @@
         <v>24.2</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1211101.1</v>
+        <v>87208.5</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,13 +164,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -802,10 +814,10 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="11" t="n">
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -817,7 +829,7 @@
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="11" t="n">
         <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -881,10 +893,10 @@
       <c r="K5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -896,7 +908,7 @@
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -911,7 +923,7 @@
       <c r="U5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="15" t="n">
         <v>43.9</v>
       </c>
       <c r="W5" s="3" t="n">
@@ -964,10 +976,10 @@
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="11" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -979,7 +991,7 @@
       <c r="P6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="11" t="n">
         <v>29.5</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -1035,7 +1047,7 @@
       <c r="G7" s="11" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="12" t="n">
         <v>79.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1047,10 +1059,10 @@
       <c r="K7" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="11" t="n">
         <v>20.4</v>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
@@ -1060,7 +1072,7 @@
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="11" t="n">
         <v>20.1</v>
       </c>
       <c r="R7" s="3" t="n">
@@ -1130,10 +1142,10 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
@@ -1143,7 +1155,7 @@
       <c r="P8" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="R8" s="3" t="n">
@@ -1158,7 +1170,7 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="15" t="n">
         <v>2.4</v>
       </c>
       <c r="W8" s="3" t="n">
@@ -1208,14 +1220,14 @@
       <c r="J9" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="16" t="n">
         <v>944.1</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="11" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="M9" s="11" t="n">
         <v>92.8</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>100.1</v>
@@ -1226,10 +1238,10 @@
       <c r="P9" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="3" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="R9" s="3" t="n">
+      <c r="Q9" s="11" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="R9" s="16" t="n">
         <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1241,10 +1253,10 @@
       <c r="U9" s="3" t="n">
         <v>48.8</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="16" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="16" t="n">
         <v>11</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1279,7 +1291,7 @@
       <c r="F10" s="11" t="n">
         <v>23.5</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="12" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1294,10 +1306,10 @@
       <c r="K10" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1309,10 +1321,10 @@
       <c r="P10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="16" t="n">
         <v>22</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1324,10 +1336,10 @@
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="16" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="16" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1368,7 +1380,7 @@
       <c r="H11" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="12" t="n">
         <v>11.8</v>
       </c>
       <c r="J11" s="3" t="n">
@@ -1377,10 +1389,10 @@
       <c r="K11" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="15" t="n">
         <v>0.7</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1393,7 +1405,7 @@
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="15" t="n">
         <v>2.3</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1408,7 +1420,7 @@
       <c r="V11" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="11" t="n">
         <v>22.7</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1491,7 +1503,7 @@
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="11" t="n">
         <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1541,7 +1553,7 @@
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="12" t="n">
         <v>19.2</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1574,7 +1586,7 @@
       <c r="V13" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="11" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1652,10 +1664,10 @@
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V14" s="8" t="n">
+      <c r="V14" s="12" t="n">
         <v>15.1</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1722,13 +1734,13 @@
       <c r="P15" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="15" t="n">
         <v>2.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="12" t="n">
         <v>22.7</v>
       </c>
       <c r="T15" s="3" t="n">
@@ -1740,7 +1752,7 @@
       <c r="V15" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1766,13 +1778,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="16" t="n">
         <v>1940.4</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="16" t="n">
         <v>44.3</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="16" t="n">
         <v>114.6</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1787,13 +1799,13 @@
       <c r="J16" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="16" t="n">
         <v>3.2</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="16" t="n">
         <v>951.3</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="16" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1805,10 +1817,10 @@
       <c r="P16" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="16" t="n">
         <v>122.2</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="16" t="n">
         <v>1127.3</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1820,11 +1832,11 @@
       <c r="U16" s="3" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="16" t="n">
         <v>984.8</v>
       </c>
-      <c r="W16" s="3" t="n">
-        <v>1124.6</v>
+      <c r="W16" s="11" t="n">
+        <v>107.5</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
@@ -1845,13 +1857,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="16" t="n">
         <v>29.9</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="16" t="n">
         <v>19.3</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="16" t="n">
         <v>23.3</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1867,10 +1879,10 @@
         <v>4.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="16" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="16" t="n">
         <v>18.3</v>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
@@ -1880,13 +1892,13 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q17" s="16" t="n">
         <v>51.8</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="16" t="n">
         <v>22.5</v>
       </c>
-      <c r="S17" s="8" t="n">
+      <c r="S17" s="12" t="n">
         <v>35.3</v>
       </c>
       <c r="T17" s="3" t="n">
@@ -1895,10 +1907,10 @@
       <c r="U17" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="16" t="n">
         <v>22.7</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1946,10 +1958,10 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
@@ -2027,7 +2039,7 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="11" t="n">
         <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2106,7 +2118,7 @@
       <c r="K20" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="11" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2121,7 +2133,7 @@
       <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="15" t="n">
         <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
@@ -2136,7 +2148,7 @@
       <c r="U20" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="15" t="n">
         <v>81.8</v>
       </c>
       <c r="W20" s="3" t="n">
@@ -2163,7 +2175,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="15" t="n">
         <v>1.5</v>
       </c>
       <c r="E21" s="3" t="n">
@@ -2187,7 +2199,7 @@
       <c r="K21" s="3" t="n">
         <v>73.8</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="11" t="n">
         <v>19.4</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2203,7 +2215,7 @@
       <c r="Q21" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="15" t="n">
         <v>1.9</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2243,10 +2255,10 @@
       <c r="D22" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="15" t="n">
         <v>1.7</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="12" t="n">
         <v>32.8</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2264,7 +2276,7 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="11" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
@@ -2282,7 +2294,7 @@
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="15" t="n">
         <v>2.3</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2321,13 +2333,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="16" t="n">
         <v>194.4</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="16" t="n">
         <v>10.4</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="16" t="n">
         <v>119.2</v>
       </c>
       <c r="G23" s="3" t="n">
@@ -2342,13 +2354,13 @@
       <c r="J23" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="16" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="11" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="16" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2358,10 +2370,10 @@
         <v>43.1</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="16" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="16" t="n">
         <v>107.9</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2373,10 +2385,10 @@
       <c r="U23" s="3" t="n">
         <v>47.9</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="16" t="n">
         <v>108.6</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="16" t="n">
         <v>19.7</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2422,10 +2434,10 @@
         <v>2.8</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="M24" s="8" t="n">
+      <c r="L24" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M24" s="16" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
@@ -2435,13 +2447,13 @@
       <c r="P24" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="16" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="16" t="n">
         <v>21</v>
       </c>
-      <c r="S24" s="8" t="n">
+      <c r="S24" s="12" t="n">
         <v>823.9</v>
       </c>
       <c r="T24" s="3" t="n">
@@ -2450,10 +2462,10 @@
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="16" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="16" t="n">
         <v>20.5</v>
       </c>
       <c r="X24" s="3" t="inlineStr"/>
@@ -2499,10 +2511,10 @@
       <c r="K25" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="15" t="n">
         <v>42.4</v>
       </c>
-      <c r="M25" s="3" t="inlineStr"/>
+      <c r="M25" s="13" t="inlineStr"/>
       <c r="N25" s="3" t="n">
         <v>1.4</v>
       </c>
@@ -2533,7 +2545,7 @@
       <c r="W25" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="12" t="n">
         <v>71.3</v>
       </c>
       <c r="Y25" s="3" t="n">
@@ -2663,7 +2675,7 @@
       <c r="M27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="12" t="n">
         <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
@@ -2672,7 +2684,7 @@
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="15" t="n">
         <v>2.6</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2690,7 +2702,7 @@
       <c r="V27" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W27" s="3" t="inlineStr"/>
+      <c r="W27" s="13" t="inlineStr"/>
       <c r="X27" s="3" t="n">
         <v>80.2</v>
       </c>
@@ -2754,7 +2766,7 @@
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="15" t="n">
         <v>2.3</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2769,7 +2781,7 @@
       <c r="V28" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="12" t="n">
         <v>22.8</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2820,7 +2832,7 @@
       <c r="L29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="15" t="n">
         <v>1.2</v>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
@@ -2893,13 +2905,13 @@
       <c r="J30" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="16" t="n">
         <v>3.3</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="16" t="n">
         <v>92.5</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="16" t="n">
         <v>96.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
@@ -2909,10 +2921,10 @@
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="16" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="16" t="n">
         <v>112.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2924,10 +2936,10 @@
       <c r="U30" s="3" t="n">
         <v>118.2</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="16" t="n">
         <v>18.4</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="16" t="n">
         <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -2973,10 +2985,10 @@
         <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="16" t="n">
         <v>10.3</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="16" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -2988,10 +3000,10 @@
       <c r="P31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="16" t="n">
         <v>26.3</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="16" t="n">
         <v>82.8</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3003,10 +3015,10 @@
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="16" t="n">
         <v>25.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="16" t="n">
         <v>22.8</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3033,7 +3045,7 @@
       <c r="D32" s="3" t="n">
         <v>34.8</v>
       </c>
-      <c r="E32" s="14" t="n">
+      <c r="E32" s="15" t="n">
         <v>1.8</v>
       </c>
       <c r="F32" s="3" t="n">
@@ -3067,10 +3079,10 @@
       <c r="P32" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="11" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3085,7 +3097,7 @@
       <c r="V32" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3107,13 +3119,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="15" t="n">
         <v>4.2</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="15" t="n">
         <v>2.5</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3131,7 +3143,7 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="L33" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3144,10 +3156,10 @@
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="11" t="n">
         <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3162,7 +3174,7 @@
       <c r="V33" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="11" t="n">
         <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3213,7 +3225,7 @@
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="15" t="n">
         <v>91.90000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3225,10 +3237,10 @@
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3243,7 +3255,7 @@
       <c r="V34" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3306,10 +3318,10 @@
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3324,7 +3336,7 @@
       <c r="V35" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="11" t="n">
         <v>24.2</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3348,7 +3360,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="14" t="n">
+      <c r="D36" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="E36" s="3" t="n">
@@ -3375,7 +3387,7 @@
       <c r="L36" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="N36" s="3" t="inlineStr"/>
@@ -3385,10 +3397,10 @@
       <c r="P36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="11" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="11" t="n">
         <v>23</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3403,7 +3415,7 @@
       <c r="V36" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="11" t="n">
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3430,7 +3442,7 @@
       <c r="D37" s="11" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="16" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="F37" s="11" t="n">
@@ -3448,13 +3460,13 @@
       <c r="J37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="16" t="n">
         <v>949.9</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="16" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="16" t="n">
         <v>92</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3466,11 +3478,11 @@
       <c r="P37" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="11" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="3" t="n">
-        <v>119</v>
+      <c r="R37" s="11" t="n">
+        <v>118.5</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>1230.4</v>
@@ -3481,11 +3493,11 @@
       <c r="U37" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="16" t="n">
         <v>115</v>
       </c>
-      <c r="W37" s="3" t="n">
-        <v>129.9</v>
+      <c r="W37" s="11" t="n">
+        <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3530,10 +3542,10 @@
         <v>9.9</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="16" t="n">
         <v>14.8</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="16" t="n">
         <v>46.8</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3545,10 +3557,10 @@
       <c r="P38" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3560,10 +3572,10 @@
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="16" t="n">
         <v>22.2</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3614,7 +3626,7 @@
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
@@ -3627,7 +3639,7 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="15" t="n">
         <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3703,10 +3715,10 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="8" t="n">
+      <c r="Q40" s="12" t="n">
         <v>31.2</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="15" t="n">
         <v>82.2</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3748,7 +3760,7 @@
       <c r="D41" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="E41" s="14" t="n">
+      <c r="E41" s="15" t="n">
         <v>17.9</v>
       </c>
       <c r="F41" s="3" t="n">
@@ -3795,7 +3807,7 @@
       <c r="U41" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="15" t="n">
         <v>2.4</v>
       </c>
       <c r="W41" s="3" t="n">
@@ -3825,7 +3837,7 @@
       <c r="D42" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="E42" s="14" t="n">
+      <c r="E42" s="15" t="n">
         <v>32.8</v>
       </c>
       <c r="F42" s="3" t="n">
@@ -3846,7 +3858,7 @@
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="15" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -3862,7 +3874,7 @@
       <c r="Q42" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="15" t="n">
         <v>82</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -3874,8 +3886,8 @@
       <c r="U42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V42" s="3" t="inlineStr"/>
-      <c r="W42" s="3" t="inlineStr"/>
+      <c r="V42" s="13" t="inlineStr"/>
+      <c r="W42" s="13" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -3895,26 +3907,26 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
-      <c r="F43" s="12" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr"/>
+      <c r="F43" s="13" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="13" t="inlineStr"/>
+      <c r="L43" s="13" t="inlineStr"/>
+      <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
+      <c r="R43" s="13" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
+      <c r="V43" s="13" t="inlineStr"/>
+      <c r="W43" s="13" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -3934,26 +3946,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="12" t="inlineStr"/>
+      <c r="D44" s="13" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="K44" s="13" t="inlineStr"/>
+      <c r="L44" s="13" t="inlineStr"/>
+      <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="R44" s="13" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="13" t="inlineStr"/>
+      <c r="W44" s="13" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -3971,13 +3983,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="16" t="n">
         <v>122.3</v>
       </c>
-      <c r="E45" s="13" t="n">
+      <c r="E45" s="16" t="n">
         <v>24.6</v>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="F45" s="16" t="n">
         <v>162</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -3992,13 +4004,13 @@
       <c r="J45" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="16" t="n">
         <v>2.8</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="16" t="n">
         <v>141.1</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="16" t="n">
         <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4010,8 +4022,8 @@
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="n">
+      <c r="Q45" s="14" t="inlineStr"/>
+      <c r="R45" s="16" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4023,10 +4035,10 @@
       <c r="U45" s="3" t="n">
         <v>95.2</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="16" t="n">
         <v>22.9</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="16" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4068,16 +4080,16 @@
       <c r="I46" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="J46" s="8" t="n">
+      <c r="J46" s="12" t="n">
         <v>4.1</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="L46" s="8" t="n">
+      <c r="L46" s="16" t="n">
         <v>42.7</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="16" t="n">
         <v>11.9</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4090,7 +4102,7 @@
         <v>0.2</v>
       </c>
       <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="16" t="n">
         <v>22.9</v>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -4100,10 +4112,10 @@
       <c r="U46" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="16" t="n">
         <v>21.8</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="16" t="n">
         <v>24.2</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -820,13 +820,13 @@
       <c r="M4" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="N4" s="11" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O4" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P4" s="11" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="11" t="n">
@@ -899,13 +899,13 @@
       <c r="M5" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="N5" s="11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="11" t="n">
@@ -982,14 +982,14 @@
       <c r="M6" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>2</v>
+      <c r="N6" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>-0.1</v>
       </c>
       <c r="Q6" s="11" t="n">
         <v>29.5</v>
@@ -1065,26 +1065,28 @@
       <c r="M7" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0.2</v>
+      <c r="N7" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>-0.1</v>
       </c>
       <c r="Q7" s="11" t="n">
         <v>20.1</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="S7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="U7" s="3" t="n">
+      <c r="S7" s="11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="T7" s="11" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="U7" s="11" t="n">
         <v>0.9</v>
       </c>
       <c r="V7" s="3" t="n">
@@ -1148,12 +1150,14 @@
       <c r="M8" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>8</v>
+      <c r="N8" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="Q8" s="11" t="n">
         <v>25.8</v>
@@ -1312,14 +1316,14 @@
       <c r="M10" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.1</v>
+      <c r="N10" s="11" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="Q10" s="11" t="n">
         <v>25.9</v>
@@ -2042,14 +2046,16 @@
       <c r="L19" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="P19" s="3" t="n">
+      <c r="N19" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>99</v>
+      </c>
+      <c r="P19" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
@@ -2121,16 +2127,16 @@
       <c r="L20" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="P20" s="3" t="n">
+      <c r="N20" s="11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P20" s="11" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="15" t="n">
@@ -2279,16 +2285,16 @@
       <c r="L22" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="P22" s="3" t="n">
+      <c r="N22" s="11" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
@@ -3085,14 +3091,14 @@
       <c r="R32" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>15.5</v>
+      <c r="S32" s="11" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="T32" s="11" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="U32" s="11" t="n">
+        <v>12.4</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>22.2</v>
@@ -3162,14 +3168,14 @@
       <c r="R33" s="11" t="n">
         <v>27.8</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>15</v>
+      <c r="S33" s="11" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="T33" s="11" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="U33" s="11" t="n">
+        <v>2.5</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>29.2</v>
@@ -3243,14 +3249,14 @@
       <c r="R34" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="S34" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>2</v>
+      <c r="S34" s="11" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="T34" s="11" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="U34" s="11" t="n">
+        <v>6.6</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3324,14 +3330,14 @@
       <c r="R35" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="S35" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>192.2</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>2.5</v>
+      <c r="S35" s="11" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="T35" s="11" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="U35" s="11" t="n">
+        <v>10.1</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>32</v>
@@ -3403,14 +3409,14 @@
       <c r="R36" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>2.8</v>
+      <c r="S36" s="11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="T36" s="11" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="U36" s="11" t="n">
+        <v>17.4</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>23.9</v>
@@ -3563,14 +3569,14 @@
       <c r="R38" s="11" t="n">
         <v>23.5</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>24.9</v>
+      <c r="S38" s="11" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="T38" s="11" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="U38" s="11" t="n">
+        <v>10.2</v>
       </c>
       <c r="V38" s="16" t="n">
         <v>22.2</v>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,16 +164,22 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -814,19 +820,19 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="N4" s="11" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="O4" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P4" s="11" t="n">
+      <c r="N4" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="11" t="n">
@@ -836,22 +842,26 @@
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>25.2</v>
+        <v>2.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>45.2</v>
+        <v>4.5</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="W4" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W4" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>7.6</v>
+      </c>
       <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -866,46 +876,44 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>26.8</v>
+      <c r="F5" s="11" t="n">
+        <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>17.6</v>
+        <v>8</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="N5" s="11" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P5" s="11" t="n">
+      <c r="N5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="11" t="n">
@@ -918,22 +926,22 @@
         <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>10.2</v>
+        <v>70.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V5" s="15" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="W5" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="W5" s="11" t="n">
         <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>16.2</v>
+        <v>76.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -952,14 +960,14 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>27.6</v>
+      <c r="D6" s="11" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>24.6</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15.2</v>
@@ -971,25 +979,23 @@
         <v>2.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="n">
+        <v>921.2</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>20</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="P6" s="11" t="n">
-        <v>-0.1</v>
       </c>
       <c r="Q6" s="11" t="n">
         <v>29.5</v>
@@ -1001,25 +1007,25 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>20.6</v>
+        <v>390.6</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>14.4</v>
+        <v>17.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>21.3</v>
+      <c r="W6" s="11" t="n">
+        <v>22.6</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>17.8</v>
+        <v>27.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>4</v>
+        <v>24.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1047,8 +1053,8 @@
       <c r="G7" s="11" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="12" t="n">
-        <v>79.8</v>
+      <c r="H7" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1057,22 +1063,22 @@
         <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L7" s="11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="P7" s="11" t="n">
-        <v>-0.1</v>
+        <v>20.2</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q7" s="11" t="n">
         <v>20.1</v>
@@ -1092,17 +1098,17 @@
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="11" t="n">
         <v>20.6</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>86.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1117,9 +1123,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="11" t="n">
         <v>26.8</v>
       </c>
@@ -1136,7 +1140,7 @@
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.2</v>
@@ -1144,19 +1148,17 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M8" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="N8" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P8" s="11" t="n">
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="n">
+        <v>791.2</v>
+      </c>
+      <c r="P8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="11" t="n">
@@ -1169,25 +1171,25 @@
         <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>6.6</v>
+        <v>66.2</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W8" s="3" t="n">
+      <c r="V8" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W8" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>69.2</v>
+        <v>86.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.3</v>
+        <v>27.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1204,40 +1206,40 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="11" t="n">
-        <v>147.4</v>
+        <v>147.5</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>89.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>54.8</v>
+        <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>944.1</v>
-      </c>
-      <c r="L9" s="11" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="L9" s="18" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>100.1</v>
+        <v>1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>452.5</v>
+        <v>451.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1245,11 +1247,11 @@
       <c r="Q9" s="11" t="n">
         <v>129.9</v>
       </c>
-      <c r="R9" s="16" t="n">
-        <v>110.9</v>
+      <c r="R9" s="18" t="n">
+        <v>110.1</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122</v>
+        <v>122.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
@@ -1257,19 +1259,21 @@
       <c r="U9" s="3" t="n">
         <v>48.8</v>
       </c>
-      <c r="V9" s="16" t="n">
+      <c r="V9" s="18" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="16" t="n">
-        <v>11</v>
+      <c r="W9" s="11" t="n">
+        <v>110.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="Z9" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1283,77 +1287,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="11" t="n">
         <v>29.5</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>91.59999999999999</v>
+        <v>23.7</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>11.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L10" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="18" t="n">
         <v>18.5</v>
       </c>
       <c r="M10" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="N10" s="11" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P10" s="11" t="n">
-        <v>0</v>
+      <c r="N10" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q10" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="16" t="n">
+      <c r="R10" s="18" t="n">
         <v>22</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V10" s="16" t="n">
+      <c r="V10" s="18" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="16" t="n">
+      <c r="W10" s="11" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.2</v>
+        <v>62.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1370,10 +1372,10 @@
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="11" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>23.8</v>
@@ -1381,51 +1383,47 @@
       <c r="G11" s="11" t="n">
         <v>10.5</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="L11" s="15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>18.3</v>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>24.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>91.59999999999999</v>
+      </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="15" t="n">
-        <v>2.3</v>
+      <c r="R11" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
+        <v>28.9</v>
       </c>
       <c r="W11" s="11" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>26.8</v>
@@ -1433,7 +1431,9 @@
       <c r="Y11" s="3" t="n">
         <v>81.2</v>
       </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1447,9 +1447,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="11" t="n">
         <v>26.5</v>
       </c>
@@ -1459,38 +1457,38 @@
       <c r="F12" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>89.40000000000001</v>
+      <c r="G12" s="15" t="n">
+        <v>98.40000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>19</v>
+        <v>8.6</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>1.9</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22.6</v>
+        <v>2.5</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>24.2</v>
+        <v>8.4</v>
+      </c>
+      <c r="Q12" s="15" t="n">
+        <v>2.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
@@ -1499,25 +1497,25 @@
         <v>2.5</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W12" s="11" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>24.4</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>83.2</v>
+        <v>81.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>6.5</v>
+        <v>82.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1537,13 +1535,13 @@
         <v>26.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.9</v>
+        <v>89.3</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>17.6</v>
@@ -1552,22 +1550,22 @@
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="12" t="n">
-        <v>19.2</v>
+      <c r="L13" s="17" t="n">
+        <v>19.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>24.3</v>
+        <v>0.4</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.4</v>
@@ -1585,7 +1583,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3.8</v>
+        <v>31.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1597,10 +1595,10 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>85.2</v>
+        <v>12</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1615,7 +1613,9 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D14" s="11" t="n">
         <v>29.9</v>
       </c>
@@ -1629,24 +1629,26 @@
         <v>19.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>20.7</v>
+        <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
       </c>
@@ -1660,16 +1662,16 @@
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.6</v>
+        <v>25.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>88.2</v>
+        <v>58.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V14" s="12" t="n">
-        <v>15.1</v>
+      <c r="V14" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="W14" s="11" t="n">
         <v>22.8</v>
@@ -1678,7 +1680,7 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>717.2</v>
+        <v>27.2</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>51.4</v>
@@ -1696,32 +1698,30 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="11" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="E15" s="11" t="n">
         <v>18.6</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="17" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.5</v>
+        <v>9.6</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
@@ -1730,13 +1730,13 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>29.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.5</v>
+        <v>91.2</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" s="15" t="n">
         <v>2.6</v>
@@ -1744,8 +1744,8 @@
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="12" t="n">
-        <v>22.7</v>
+      <c r="S15" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1754,7 +1754,7 @@
         <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>21.4</v>
+        <v>28.4</v>
       </c>
       <c r="W15" s="11" t="n">
         <v>20.9</v>
@@ -1766,7 +1766,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1782,71 +1782,73 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="16" t="n">
-        <v>1940.4</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>114.6</v>
+      <c r="D16" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>48.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.5</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K16" s="16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L16" s="16" t="n">
-        <v>951.3</v>
-      </c>
-      <c r="M16" s="16" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="18" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="M16" s="18" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>453.2</v>
+        <v>853.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q16" s="16" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="R16" s="16" t="n">
-        <v>1127.3</v>
+        <v>1.4</v>
+      </c>
+      <c r="Q16" s="18" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="R16" s="18" t="n">
+        <v>122.3</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>18.2</v>
+        <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="V16" s="16" t="n">
-        <v>984.8</v>
+        <v>99.2</v>
+      </c>
+      <c r="V16" s="18" t="n">
+        <v>187.8</v>
       </c>
       <c r="W16" s="11" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="X16" s="3" t="inlineStr"/>
+        <v>108.5</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>124.6</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>10064.6</v>
-      </c>
-      <c r="Z16" s="3" t="inlineStr"/>
+        <v>970.8</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1861,17 +1863,17 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="16" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>23.3</v>
+      <c r="D17" s="18" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>1.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.5</v>
@@ -1880,39 +1882,41 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4.8</v>
+        <v>22.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="16" t="n">
+      <c r="L17" s="18" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="16" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+      <c r="M17" s="18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>9.1</v>
+        <v>21.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="16" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="R17" s="16" t="n">
+      <c r="Q17" s="18" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R17" s="18" t="n">
         <v>22.5</v>
       </c>
-      <c r="S17" s="12" t="n">
-        <v>35.3</v>
+      <c r="S17" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="V17" s="16" t="n">
-        <v>22.7</v>
+        <v>82.2</v>
+      </c>
+      <c r="V17" s="18" t="n">
+        <v>22.9</v>
       </c>
       <c r="W17" s="11" t="n">
         <v>21.5</v>
@@ -1921,9 +1925,11 @@
         <v>24.8</v>
       </c>
       <c r="Y17" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="Z17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1938,45 +1944,47 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>25.9</v>
+      <c r="D18" s="11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>19.4</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M18" s="15" t="n">
         <v>1.3</v>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O18" s="3" t="n">
-        <v>91.2</v>
+        <v>291.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="3" t="n">
-        <v>29.2</v>
+      <c r="Q18" s="15" t="n">
+        <v>89.2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.2</v>
@@ -1985,10 +1993,10 @@
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>94.2</v>
+        <v>54.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.4</v>
+        <v>1</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21.8</v>
@@ -1997,12 +2005,14 @@
         <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>24.3</v>
+        <v>25.3</v>
       </c>
       <c r="Y18" s="3" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="Z18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -2017,25 +2027,25 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>30.6</v>
+        <v>30.3</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="G19" s="11" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>46.9</v>
+        <v>15.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>2.5</v>
@@ -2043,19 +2053,19 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M19" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N19" s="11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="O19" s="11" t="n">
-        <v>99</v>
-      </c>
-      <c r="P19" s="11" t="n">
+      <c r="M19" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P19" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
@@ -2071,21 +2081,23 @@
         <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>19.9</v>
+        <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z19" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2099,18 +2111,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>9.6</v>
+      <c r="C20" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>59.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2122,21 +2136,19 @@
         <v>2.8</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" s="11" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M20" s="11" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N20" s="11" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="O20" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="15" t="n">
@@ -2146,27 +2158,29 @@
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>22.7</v>
+        <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>72.2</v>
+        <v>22.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V20" s="15" t="n">
-        <v>81.8</v>
+      <c r="V20" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X20" s="3" t="n">
-        <v>22.1</v>
+      <c r="X20" s="17" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="n">
+        <v>21.1</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2180,21 +2194,23 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>21.2</v>
+      <c r="C21" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>23.4</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.7</v>
+        <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2203,9 +2219,9 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="L21" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L21" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2219,31 +2235,35 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>11.2</v>
+        <v>19.2</v>
       </c>
       <c r="R21" s="15" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.3</v>
+        <v>88.7</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="W21" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X21" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2257,15 +2277,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>32.8</v>
+      <c r="C22" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>23.6</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
@@ -2277,54 +2299,56 @@
         <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>23.2</v>
+        <v>3.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="N22" s="11" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="O22" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="11" t="n">
+      <c r="N22" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>991.2</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="n">
-        <v>28.5</v>
+      <c r="Q22" s="15" t="n">
+        <v>2.9</v>
       </c>
       <c r="R22" s="15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>8956.200000000001</v>
+        <v>86.2</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>24.6</v>
+      <c r="V22" s="15" t="n">
+        <v>2.4</v>
       </c>
       <c r="W22" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="X22" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X22" s="3" t="n">
+      <c r="Y22" s="3" t="n">
         <v>80.2</v>
       </c>
-      <c r="Y22" s="3" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2339,71 +2363,73 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="16" t="n">
-        <v>194.4</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>119.2</v>
+      <c r="D23" s="11" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>114</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>5.2</v>
+        <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>85.8</v>
+        <v>23.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K23" s="16" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="L23" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K23" s="18" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L23" s="18" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="M23" s="16" t="n">
-        <v>92.90000000000001</v>
+      <c r="M23" s="18" t="n">
+        <v>1952.9</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>43.1</v>
+        <v>951.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="16" t="n">
+      <c r="Q23" s="18" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="16" t="n">
-        <v>107.9</v>
+      <c r="R23" s="18" t="n">
+        <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>360.2</v>
+        <v>36</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="V23" s="16" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="W23" s="16" t="n">
-        <v>19.7</v>
+        <v>37.7</v>
+      </c>
+      <c r="V23" s="18" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="W23" s="18" t="n">
+        <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>94927.8</v>
+        <v>198.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Z23" s="3" t="inlineStr"/>
+        <v>9425.6</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2417,7 +2443,9 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D24" s="11" t="n">
         <v>28.5</v>
       </c>
@@ -2434,51 +2462,57 @@
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M24" s="16" t="n">
+      <c r="L24" s="18" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="M24" s="18" t="n">
         <v>18.6</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O24" s="3" t="n">
-        <v>581.2</v>
+        <v>91.2</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q24" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q24" s="18" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="S24" s="12" t="n">
-        <v>823.9</v>
+      <c r="R24" s="18" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>78.2</v>
+        <v>72.3</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="16" t="n">
+      <c r="V24" s="18" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="16" t="n">
+      <c r="W24" s="18" t="n">
         <v>20.5</v>
       </c>
-      <c r="X24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="n">
+        <v>23.5</v>
+      </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="n">
+        <v>85.8</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2492,70 +2526,72 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="11" t="n">
-        <v>60.7</v>
+        <v>29.9</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-11.5</v>
+        <v>18.8</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="G25" s="15" t="n">
+        <v>44.4</v>
+      </c>
       <c r="H25" s="3" t="n">
-        <v>1.7</v>
+        <v>17.9</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.4</v>
+        <v>34.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="15" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="M25" s="13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>12.9</v>
+      </c>
       <c r="N25" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>24.2</v>
+        <v>59.2</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>23</v>
+        <v>8</v>
+      </c>
+      <c r="Q25" s="15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R25" s="15" t="n">
+        <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V25" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="W25" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X25" s="12" t="n">
-        <v>71.3</v>
+      <c r="W25" s="15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>9.1</v>
+        <v>69.3</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2571,18 +2607,20 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
+        <v>111.6</v>
+      </c>
       <c r="D26" s="11" t="n">
-        <v>28.6</v>
+        <v>32.6</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>1.6</v>
@@ -2594,17 +2632,19 @@
         <v>1.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+        <v>19.6</v>
+      </c>
+      <c r="M26" s="15" t="n">
+        <v>98.96000000000001</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2613,10 +2653,10 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.9</v>
+        <v>17.9</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>76.2</v>
@@ -2624,11 +2664,11 @@
       <c r="U26" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>21.3</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>24.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>86.2</v>
@@ -2636,7 +2676,9 @@
       <c r="Y26" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="n">
+        <v>24.5</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2661,40 +2703,40 @@
         <v>22.4</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.9</v>
+        <v>19.8</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N27" s="12" t="n">
-        <v>11.8</v>
+      <c r="M27" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.4</v>
+        <v>922.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="15" t="n">
-        <v>2.6</v>
+      <c r="Q27" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
@@ -2703,19 +2745,23 @@
         <v>63.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V27" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V27" s="11" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="W27" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W27" s="13" t="inlineStr"/>
       <c r="X27" s="3" t="n">
-        <v>80.2</v>
+        <v>24</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="n">
+        <v>80.2</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2731,16 +2777,16 @@
       </c>
       <c r="C28" s="3" t="inlineStr"/>
       <c r="D28" s="11" t="n">
-        <v>32.7</v>
+        <v>30.7</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="11" t="n">
-        <v>16.8</v>
+      <c r="G28" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
@@ -2752,51 +2798,53 @@
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>16.2</v>
+        <v>0.3</v>
+      </c>
+      <c r="L28" s="15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M28" s="15" t="n">
+        <v>1.6</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.1</v>
+        <v>14.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1272.4</v>
+        <v>92.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R28" s="15" t="n">
-        <v>2.3</v>
+        <v>20.9</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>23.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.6</v>
+        <v>24.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>40.2</v>
+        <v>4</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W28" s="12" t="n">
-        <v>22.8</v>
+      <c r="V28" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="W28" s="15" t="n">
+        <v>2.1</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.4</v>
+        <v>21.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>14.6</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>53.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2812,25 +2860,25 @@
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="11" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="G29" s="11" t="n">
-        <v>11.7</v>
+      <c r="G29" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.5</v>
@@ -2839,14 +2887,16 @@
         <v>19.2</v>
       </c>
       <c r="M29" s="15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>40.7</v>
+        <v>90.2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>22.4</v>
@@ -2855,16 +2905,16 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>20.1</v>
+        <v>12.9</v>
+      </c>
+      <c r="V29" s="11" t="n">
+        <v>13.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
@@ -2875,7 +2925,9 @@
       <c r="Y29" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2891,16 +2943,16 @@
       </c>
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="11" t="n">
-        <v>179.5</v>
+        <v>150.8</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>59.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>119</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>58.8</v>
+        <v>5.8</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>80.59999999999999</v>
@@ -2909,29 +2961,29 @@
         <v>10.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K30" s="16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L30" s="16" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="M30" s="16" t="n">
-        <v>96.09999999999999</v>
+        <v>17.8</v>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L30" s="18" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="M30" s="18" t="n">
+        <v>392.1</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="16" t="n">
+      <c r="Q30" s="18" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="16" t="n">
-        <v>112.7</v>
+      <c r="R30" s="18" t="n">
+        <v>112.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
@@ -2942,19 +2994,21 @@
       <c r="U30" s="3" t="n">
         <v>118.2</v>
       </c>
-      <c r="V30" s="16" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="W30" s="16" t="n">
-        <v>117.6</v>
+      <c r="V30" s="11" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="W30" s="18" t="n">
+        <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>374.2</v>
+        <v>312.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="Z30" s="3" t="inlineStr"/>
+        <v>52.4</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>33</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2970,35 +3024,35 @@
       </c>
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="11" t="n">
-        <v>35.9</v>
+        <v>29.9</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.9</v>
+        <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16.1</v>
+        <v>18.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="16" t="n">
+      <c r="L31" s="18" t="n">
         <v>10.3</v>
       </c>
-      <c r="M31" s="16" t="n">
+      <c r="M31" s="18" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>25.5</v>
+        <v>28.4</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -3006,34 +3060,36 @@
       <c r="P31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="16" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="R31" s="16" t="n">
-        <v>82.8</v>
+      <c r="Q31" s="18" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="R31" s="18" t="n">
+        <v>22.6</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="16" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W31" s="16" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>77.3</v>
+      <c r="V31" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="W31" s="18" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="X31" s="17" t="n">
+        <v>47.8</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="Z31" s="3" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>23.6</v>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3047,70 +3103,76 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="n">
-        <v>34.8</v>
+      <c r="C32" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>23.28</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>25.6</v>
+        <v>4.5</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>35</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>29.1</v>
+        <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>9.6</v>
+        <v>0.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="L32" s="13" t="inlineStr"/>
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q32" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="11" t="n">
+      <c r="R32" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="S32" s="11" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="T32" s="11" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="U32" s="11" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>22.2</v>
+      <c r="S32" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V32" s="15" t="n">
+        <v>2.2</v>
       </c>
       <c r="W32" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>85.3</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3124,9 +3186,11 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="D33" s="15" t="n">
-        <v>4.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>18</v>
@@ -3149,36 +3213,36 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="L33" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>18.8</v>
+      <c r="M33" s="15" t="n">
+        <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="11" t="n">
+      <c r="Q33" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="11" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="S33" s="11" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="T33" s="11" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="U33" s="11" t="n">
-        <v>2.5</v>
+      <c r="R33" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="W33" s="11" t="n">
         <v>27.4</v>
@@ -3189,7 +3253,9 @@
       <c r="Y33" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3205,10 +3271,10 @@
       </c>
       <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="11" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="F34" s="11" t="n">
         <v>25.8</v>
@@ -3216,7 +3282,7 @@
       <c r="G34" s="11" t="n">
         <v>12.7</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H34" s="17" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3226,37 +3292,37 @@
         <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="M34" s="15" t="n">
-        <v>91.90000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q34" s="11" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R34" s="11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R34" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="S34" s="11" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="T34" s="11" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="U34" s="11" t="n">
-        <v>6.6</v>
+      <c r="S34" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3268,9 +3334,11 @@
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3284,7 +3352,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D35" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -3310,34 +3380,34 @@
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>11.1</v>
+        <v>19</v>
+      </c>
+      <c r="M35" s="15" t="n">
+        <v>1.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>172.4</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="11" t="n">
+      <c r="Q35" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="11" t="n">
+      <c r="R35" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="S35" s="11" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="T35" s="11" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="U35" s="11" t="n">
-        <v>10.1</v>
+      <c r="S35" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>32</v>
@@ -3351,7 +3421,9 @@
       <c r="Y35" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="n">
+        <v>33.6</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3366,11 +3438,11 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="15" t="n">
-        <v>1.3</v>
+      <c r="D36" s="17" t="n">
+        <v>33.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>25.8</v>
@@ -3385,38 +3457,40 @@
         <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="M36" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>70.7</v>
+        <v>90.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="S36" s="11" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="T36" s="11" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="U36" s="11" t="n">
-        <v>17.4</v>
+      <c r="R36" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>28.3</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>23.9</v>
@@ -3425,12 +3499,14 @@
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>8.5</v>
+        <v>85.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3445,73 +3521,75 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="18" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="16" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="F37" s="11" t="n">
+      <c r="E37" s="18" t="n">
+        <v>1929.5</v>
+      </c>
+      <c r="F37" s="18" t="n">
         <v>126.9</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="G37" s="3" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>81</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" s="16" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K37" s="18" t="n">
         <v>949.9</v>
       </c>
-      <c r="L37" s="16" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="M37" s="16" t="n">
-        <v>92</v>
+      <c r="L37" s="18" t="n">
+        <v>951.1</v>
+      </c>
+      <c r="M37" s="18" t="n">
+        <v>0.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.5</v>
+        <v>11.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>950.2</v>
+        <v>150.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q37" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Q37" s="18" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="11" t="n">
-        <v>118.5</v>
+      <c r="R37" s="18" t="n">
+        <v>117.3</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1230.4</v>
+        <v>120.4</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V37" s="16" t="n">
-        <v>115</v>
+        <v>124.7</v>
+      </c>
+      <c r="V37" s="18" t="n">
+        <v>111</v>
       </c>
       <c r="W37" s="11" t="n">
         <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7367.2</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>37.2</v>
       </c>
-      <c r="Z37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="n">
+        <v>247.3</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3526,16 +3604,16 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="11" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E38" s="11" t="n">
+      <c r="D38" s="18" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E38" s="18" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="11" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G38" s="11" t="n">
+      <c r="F38" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3545,41 +3623,41 @@
         <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9.9</v>
+        <v>4.1</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="16" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="M38" s="16" t="n">
-        <v>46.8</v>
+      <c r="L38" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="M38" s="18" t="n">
+        <v>17.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>0.2</v>
+        <v>18.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>30.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q38" s="11" t="n">
+      <c r="Q38" s="18" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="18" t="n">
         <v>23.5</v>
       </c>
-      <c r="S38" s="11" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="T38" s="11" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="U38" s="11" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V38" s="16" t="n">
-        <v>22.2</v>
+      <c r="S38" s="3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V38" s="18" t="n">
+        <v>82.2</v>
       </c>
       <c r="W38" s="11" t="n">
         <v>25.2</v>
@@ -3588,9 +3666,11 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3606,38 +3686,38 @@
       </c>
       <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>18.5</v>
+        <v>32.6</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>8.5</v>
+        <v>25.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H39" s="17" t="n">
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M39" s="12" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L39" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>796</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3645,29 +3725,33 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="15" t="n">
-        <v>42.6</v>
+      <c r="R39" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>25.1</v>
+        <v>22.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>69.2</v>
+        <v>61.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>27.8</v>
+        <v>21.9</v>
       </c>
       <c r="V39" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W39" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z39" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W39" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Y39" s="3" t="inlineStr"/>
-      <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3681,7 +3765,9 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D40" s="11" t="n">
         <v>32.5</v>
       </c>
@@ -3695,25 +3781,25 @@
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M40" s="3" t="n">
-        <v>13.8</v>
+      <c r="M40" s="15" t="n">
+        <v>1.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>11.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3721,34 +3807,36 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="12" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R40" s="15" t="n">
-        <v>82.2</v>
+      <c r="Q40" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>26</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>19.2</v>
+        <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y40" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V40" s="11" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="W40" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X40" s="11" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y40" s="11" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="Z40" s="11" t="n">
+        <v>826.2</v>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3763,43 +3851,45 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F41" s="3" t="n">
+      <c r="D41" s="11" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F41" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>20.9</v>
+        <v>0</v>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>9.1</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
+        <v>81.2</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="Q41" s="3" t="n">
-        <v>2.4</v>
+        <v>29.4</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>22.8</v>
@@ -3808,24 +3898,26 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>2.4</v>
+        <v>37.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V41" s="15" t="n">
-        <v>2.4</v>
+        <v>9</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>68.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3840,60 +3932,64 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="13" t="inlineStr"/>
+      <c r="E42" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="E42" s="15" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="F42" s="3" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="H42" s="3" t="n">
-        <v>11.8</v>
+        <v>1.3</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>8.6</v>
+      <c r="J42" s="17" t="n">
+        <v>72.8</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="15" t="n">
-        <v>98.40000000000001</v>
+      <c r="L42" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>13.3</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>25</v>
+      <c r="Q42" s="15" t="n">
+        <v>2.5</v>
       </c>
       <c r="R42" s="15" t="n">
         <v>82</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>27.6</v>
+        <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>21.4</v>
+        <v>11.6</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V42" s="13" t="inlineStr"/>
-      <c r="W42" s="13" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="V42" s="15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W42" s="15" t="n">
+        <v>0.7</v>
+      </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -3926,7 +4022,7 @@
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="Q43" s="13" t="inlineStr"/>
       <c r="R43" s="13" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
@@ -3965,7 +4061,7 @@
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="Q44" s="13" t="inlineStr"/>
       <c r="R44" s="13" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -3988,72 +4084,76 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="16" t="n">
+      <c r="C45" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" s="18" t="n">
         <v>122.3</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="18" t="n">
         <v>24.6</v>
       </c>
-      <c r="F45" s="16" t="n">
-        <v>162</v>
+      <c r="F45" s="18" t="n">
+        <v>102</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>5.4</v>
+        <v>54.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>62.8</v>
+        <v>69.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K45" s="16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L45" s="16" t="n">
-        <v>141.1</v>
-      </c>
-      <c r="M45" s="16" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>8.9</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="K45" s="18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L45" s="18" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="M45" s="18" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>26.6</v>
+        <v>2366.2</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="14" t="inlineStr"/>
-      <c r="R45" s="16" t="n">
-        <v>91.59999999999999</v>
+      <c r="Q45" s="18" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="R45" s="18" t="n">
+        <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>32.7</v>
+        <v>132.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="V45" s="16" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="W45" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V45" s="18" t="n">
+        <v>892.7</v>
+      </c>
+      <c r="W45" s="18" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>221.2</v>
+        <v>19327.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>21.4</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4068,69 +4168,75 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E46" s="18" t="n">
         <v>32.3</v>
       </c>
-      <c r="E46" s="11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>25.5</v>
-      </c>
-      <c r="G46" s="11" t="n">
-        <v>13.7</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>30.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="16" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="M46" s="16" t="n">
-        <v>11.9</v>
+        <v>0.4</v>
+      </c>
+      <c r="L46" s="18" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="M46" s="18" t="n">
+        <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>92.3</v>
       </c>
       <c r="P46" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q46" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="16" t="n">
+      <c r="R46" s="18" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
       <c r="T46" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="V46" s="18" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W46" s="18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="U46" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V46" s="16" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W46" s="16" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>82.3</v>
-      </c>
       <c r="Y46" s="3" t="n">
-        <v>87208.5</v>
-      </c>
-      <c r="Z46" s="3" t="inlineStr"/>
+        <v>60.2</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>81</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
